--- a/workspaces/btc_daily_14days/volatility/bb_pct_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_pct_14.xlsx
@@ -575,46 +575,46 @@
         <v>37</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17.7768319500603</v>
+        <v>17.7196277929622</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.05096129795254711</v>
+        <v>-0.0509168531243418</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.962002496587651</v>
+        <v>4.946248596740404</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.020559246630917</v>
+        <v>-3.010665853087467</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.850598664635648</v>
+        <v>1.844454116767579</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.5573291897407699</v>
+        <v>-0.5553103956289789</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.770992041457504</v>
+        <v>4.756100359913411</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.59696685190378</v>
+        <v>1.591889431281317</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.172001196636174</v>
+        <v>-1.167887567740912</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.732926957468109</v>
+        <v>-4.717573470638605</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4791377367123388</v>
+        <v>0.4781194778387317</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.223612487169987</v>
+        <v>3.213954472255239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.618324027560405</v>
+        <v>-2.609544334653734</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.368379707682514</v>
+        <v>-2.360498363370546</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>65</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1857460125176615</v>
+        <v>-0.185916429763239</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.491995812583454</v>
+        <v>-9.461205380264936</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.732520239338676</v>
+        <v>-3.720362842147317</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.555298263289416</v>
+        <v>2.547286591329645</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.477129378446584</v>
+        <v>0.4753005512298429</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.846291756044039</v>
+        <v>-3.833510830078296</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.391364560477527</v>
+        <v>-2.383312433327312</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.483334728452036</v>
+        <v>-7.458971762391407</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.921934505070524</v>
+        <v>-2.912017087810071</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8511162988592886</v>
+        <v>0.8486775745972253</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.6458956468348305</v>
+        <v>0.6443083210169362</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.765855993530316</v>
+        <v>3.754185382646497</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2591414627120088</v>
+        <v>0.2587749825984957</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.207624973246453</v>
+        <v>-7.183783186655369</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>65</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.724207550978512</v>
+        <v>-1.719290663473494</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-6.414367432870598</v>
+        <v>-6.392745936821974</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.6540912520433935</v>
+        <v>-0.6517222722699003</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.1428291468876</v>
+        <v>-5.125622041415511</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.602912367663087</v>
+        <v>-2.594605520024096</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.846454694928845</v>
+        <v>-3.83325012786807</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.932303501860886</v>
+        <v>-3.918883668378299</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.31893461658354</v>
+        <v>-1.314171858280375</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.463739010026181</v>
+        <v>-4.44838927221199</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.774814252297872</v>
+        <v>-3.762019958222204</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.066009784645523</v>
+        <v>-7.042120049538539</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.576080657417165</v>
+        <v>-8.547280680817721</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.456732951101174</v>
+        <v>-7.431568816250923</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.208416856805272</v>
+        <v>-7.183783186654672</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>96</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.839895013122884</v>
+        <v>5.819350737892059</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.22936662897235</v>
+        <v>4.215778654401532</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.877627457169503</v>
+        <v>4.861324827057139</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.924218597828208</v>
+        <v>2.914774365086814</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.38616373915098</v>
+        <v>2.37788990631126</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.684291320663903</v>
+        <v>2.675889580519531</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.556802308915429</v>
+        <v>1.552159552382193</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.085090024303469</v>
+        <v>-3.074133889757611</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.103437906628891</v>
+        <v>-2.09545246183518</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.088313808150133</v>
+        <v>-6.067131266731785</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.25114733368666</v>
+        <v>-5.232412118158706</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.218104011395866</v>
+        <v>-5.199488555851765</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.686064373111698</v>
+        <v>-6.662457864416496</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-6.437605684458006</v>
+        <v>-6.414552417425071</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>114</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.278491504351436</v>
+        <v>6.255252568860442</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.300427340305276</v>
+        <v>7.275330820158999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.41803097501042</v>
+        <v>10.38143004033674</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.039505293388771</v>
+        <v>7.015134502691865</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.233751626955957</v>
+        <v>1.229040842961695</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.981890643382783</v>
+        <v>-1.974447347180238</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.188736561091083</v>
+        <v>-1.184039251323853</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.657295852558157</v>
+        <v>-1.650714357769935</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.797223608911978</v>
+        <v>1.792017862881579</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06611030050270017</v>
+        <v>0.06696484092259425</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.898643929031955</v>
+        <v>-1.890575420257186</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1051786505554375</v>
+        <v>-0.1033936453819777</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3529732774687275</v>
+        <v>0.3532948459878256</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.363804135148293</v>
+        <v>2.357377407136809</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>135</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.8398950131231899</v>
+        <v>0.8347787072944115</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.191922902206009</v>
+        <v>2.183621894113315</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.985706754430879</v>
+        <v>6.959018321748424</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.63521134593816</v>
+        <v>5.614242982498439</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.83938533566316</v>
+        <v>5.817632054899732</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.138407009708196</v>
+        <v>6.116897070640746</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.087281089378294</v>
+        <v>3.076786160361813</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.104204339739795</v>
+        <v>4.090333374925606</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.816983609435987</v>
+        <v>1.811344275809383</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.26280587219717</v>
+        <v>-1.257068950200846</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.502231842091049</v>
+        <v>1.498518573551827</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.0232318052553</v>
+        <v>3.013787086911563</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.602203151451207</v>
+        <v>2.594384039400943</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6230404171208122</v>
+        <v>0.6224846196122655</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>150</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.506561679790174</v>
+        <v>1.498495253382046</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5618713413638901</v>
+        <v>0.5590554390363351</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.50253641643701</v>
+        <v>3.486825551085261</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.632113962775357</v>
+        <v>1.624567593041689</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.763447579877813</v>
+        <v>3.747751264676268</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.726716200843875</v>
+        <v>2.716343105564981</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.645963854551439</v>
+        <v>4.628693304696128</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8389053271328564</v>
+        <v>0.8362510471062166</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1095881483517473</v>
+        <v>0.1099479204685991</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.411674228400969</v>
+        <v>-1.404897005879846</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2805031873111901</v>
+        <v>-0.2777720287383261</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2458416082562707</v>
+        <v>-0.2436877806651481</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.674908178911352</v>
+        <v>-2.663387547266957</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4178933965145006</v>
+        <v>-0.4145524174244528</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.529550185537282</v>
+        <v>1.53421163445131</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.381539294110418</v>
+        <v>-2.386038667553329</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.626808764235697</v>
+        <v>-1.628470241523068</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.379180680838019</v>
+        <v>1.382971911911397</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.265380259599965</v>
+        <v>0.2670966914154889</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.01272339580977189</v>
+        <v>-0.01247689874258384</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.824930494473577</v>
+        <v>-1.828484691924466</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-4.021971124425448</v>
+        <v>-4.030543245080587</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.236895461809674</v>
+        <v>-5.248199551270275</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.244345133095095</v>
+        <v>-7.260329026818304</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.146221507060346</v>
+        <v>-5.157883971238789</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.266349917500925</v>
+        <v>-6.280079298021995</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.537082537770225</v>
+        <v>-5.549613302822408</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.534967365099355</v>
+        <v>-5.547500394303221</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>163</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.9596959889217729</v>
+        <v>-0.9592163137080902</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.337492853424038</v>
+        <v>2.328048911177639</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.739762277283006</v>
+        <v>-1.736055274296064</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3817394458763275</v>
+        <v>-0.3823714456253953</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3078558277314869</v>
+        <v>0.3043139569715123</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.6236616168307805</v>
+        <v>-0.6217778720451577</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.135122197411533</v>
+        <v>1.130638516796083</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05157461764146376</v>
+        <v>0.05264674592490337</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.910577277656728</v>
+        <v>4.89347476079223</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.827758421280414</v>
+        <v>2.8201559258247</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7768277345124019</v>
+        <v>0.776809366487285</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8115891545206964</v>
+        <v>0.8111598061385834</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.621033399639657</v>
+        <v>1.61793483925603</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.48759887472243</v>
+        <v>2.481153104047792</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>183</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.220214276494247</v>
+        <v>-2.214483163411245</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.0866958704135</v>
+        <v>1.081284194574692</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1455317041337949</v>
+        <v>0.1419100997227147</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.011093810377552</v>
+        <v>2.996405261525176</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2627028097338311</v>
+        <v>-0.2643143177305092</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.129229752090403</v>
+        <v>1.124113867504285</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5980427147875389</v>
+        <v>-0.5959169773213944</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.067553174212783</v>
+        <v>-1.061741866709532</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.772859325385447</v>
+        <v>-2.760331427277151</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.435637572811117</v>
+        <v>-1.42657444721538</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.738544622845652</v>
+        <v>-2.724078748785608</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.447550402589599</v>
+        <v>-5.42223760806484</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.420722080998189</v>
+        <v>-6.39104970598504</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.426246529956231</v>
+        <v>-3.409087936550158</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.979626165513722</v>
+        <v>-4.98600517908023</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.17199241665088</v>
+        <v>-2.174796773828113</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.673263934715607</v>
+        <v>-3.677606453513853</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.990843581857021</v>
+        <v>-2.994175698129396</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.31782513625496</v>
+        <v>-1.318787788908018</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.300029831174847</v>
+        <v>2.303778562335971</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5527992257955177</v>
+        <v>-0.5535564464475229</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6391137841004308</v>
+        <v>0.6394266468786967</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.084396428295797</v>
+        <v>-1.086718718074245</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.38505299872471</v>
+        <v>-1.388495653961066</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6263344773851998</v>
+        <v>0.625783352280159</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.667959249060402</v>
+        <v>-2.673602807222785</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.332564583651383</v>
+        <v>3.335726250299238</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.362678259567005</v>
+        <v>1.363225360353169</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.273926125088025</v>
+        <v>-1.286489808345671</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.886551921109209</v>
+        <v>-2.928305943166976</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-8.442555544857036</v>
+        <v>-8.563834471868454</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.654842104305857</v>
+        <v>-4.717052446749051</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.581732669781289</v>
+        <v>-4.642730413516169</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3201254733125296</v>
+        <v>0.3305666784620982</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.813370749092577</v>
+        <v>-2.85660845433965</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.272393651016181</v>
+        <v>-3.329435768168132</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.555187637478596</v>
+        <v>-4.634271592507652</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1082504901433126</v>
+        <v>0.09363845160309836</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.541991544921146</v>
+        <v>-2.597005476791793</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.541254912515654</v>
+        <v>-1.585634045588286</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.95871105862232</v>
+        <v>-2.00588865653333</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.326248986009958</v>
+        <v>-2.3772853366794</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>178</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-10.35860685953582</v>
+        <v>-10.3252897780605</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-11.97518765025566</v>
+        <v>-11.93513022821162</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.12205486750869</v>
+        <v>-10.0884812703241</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.308854998974745</v>
+        <v>-8.282282110380876</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.913737130827876</v>
+        <v>-4.898568041248005</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.24087816620326</v>
+        <v>-1.238057103437384</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.82896734370992</v>
+        <v>-5.808904671110255</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.485793342801308</v>
+        <v>-3.471933021754047</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.859636407959364</v>
+        <v>-1.850437557216267</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.840976081001919</v>
+        <v>-3.824383943340294</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.357879800298491</v>
+        <v>-2.345818026438501</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.579025856959966</v>
+        <v>-4.558625880329018</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.436251605716393</v>
+        <v>-4.417082738464927</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.876404651987187</v>
+        <v>-5.85275466461561</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.829008790008629</v>
+        <v>-2.863433654347872</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.614330342147561</v>
+        <v>3.644127561538355</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.562268203308179</v>
+        <v>4.604864968177637</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.007809712836426</v>
+        <v>2.027304548405539</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.837671654342799</v>
+        <v>1.858189515791949</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.459955762075595</v>
+        <v>1.479510890635396</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7095193204432846</v>
+        <v>0.7106179096837337</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.263452858035976</v>
+        <v>2.277630187499135</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8586099762081219</v>
+        <v>0.8560677708962388</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6595445434710143</v>
+        <v>-0.6828780538447887</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.166225121981299</v>
+        <v>-3.2171778063055</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.800260818234015</v>
+        <v>-3.863066757803452</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8539882502203042</v>
+        <v>-0.8819608245308288</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.298755552790666</v>
+        <v>-3.353327927628683</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.829008790008629</v>
+        <v>-2.843671854625718</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.428493473051361</v>
+        <v>-7.463831179709807</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.453635162253583</v>
+        <v>-2.466006292985284</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.684686784234565</v>
+        <v>-5.709840817180627</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.235822287763391</v>
+        <v>-8.270896478338493</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-10.62785101819777</v>
+        <v>-10.67209633055863</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.695526806119886</v>
+        <v>-8.735965172618201</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.130619762236954</v>
+        <v>-5.156740790339953</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.865513384186109</v>
+        <v>-5.895842120853786</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.385806353729599</v>
+        <v>-7.425000323135187</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.570566189842133</v>
+        <v>-5.602726620425592</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.206800323268993</v>
+        <v>-6.244019138756144</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.972748019697249</v>
+        <v>-8.015625101052088</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.741663239644858</v>
+        <v>-9.792930795802832</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.510591785320123</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4818235273772942</v>
+        <v>-0.4910235768966587</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1520545528144694</v>
+        <v>-0.155957769089774</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.348755168213124</v>
+        <v>-0.3532557274165953</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.289857109537685</v>
+        <v>1.294501091160441</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.584178597908625</v>
+        <v>1.591061058554544</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.23239997141944</v>
+        <v>2.237468346449809</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.670384798844111</v>
+        <v>4.688017097395537</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.370092848618256</v>
+        <v>-3.39614054274778</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5842631341112394</v>
+        <v>-0.599196417039316</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.965892849162017</v>
+        <v>-2.993730763254867</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7501385524319701</v>
+        <v>-0.7695665840112937</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4440185750239536</v>
+        <v>-0.459894187657099</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.646297294678533</v>
+        <v>-1.670026869979516</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>149</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.54011872676989</v>
+        <v>2.536734840801287</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.75601864458347</v>
+        <v>-1.749022283186925</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.479746411582745</v>
+        <v>-1.475032896923764</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.020634218572638</v>
+        <v>-2.014886717590841</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.559055433645042</v>
+        <v>-2.55262673607303</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.603895375123855</v>
+        <v>-3.595512237671635</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3377407623838025</v>
+        <v>0.3396438935998773</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.489721188931391</v>
+        <v>-3.479621914229398</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.86580019087625</v>
+        <v>-0.8595435088726475</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.73841979251489</v>
+        <v>-3.724655683193077</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5810374645599339</v>
+        <v>-0.5737043095240821</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5476804744799892</v>
+        <v>-0.5393211521788075</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.313199813239997</v>
+        <v>-2.301857642318495</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.391188172811134</v>
+        <v>-1.380995370444737</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.530495585107843</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.297783017511584</v>
+        <v>-2.341156778480283</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.09024208555396</v>
+        <v>-2.122153931288594</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7551696758380899</v>
+        <v>-0.772055141000898</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.718457301860902</v>
+        <v>1.730936590158436</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.803377868857183</v>
+        <v>-2.839461676075445</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7437604711871728</v>
+        <v>-0.7657962512382568</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.222585448965283</v>
+        <v>-4.284656723543158</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.870573642225871</v>
+        <v>-1.915063717146779</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.150314231027806</v>
+        <v>-1.195600191296172</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.456779670558781</v>
+        <v>0.4289147770691102</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.31285520019825</v>
+        <v>-1.365970358268392</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.07753292279190305</v>
+        <v>0.04304332346991657</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9316048276928015</v>
+        <v>0.9025207533070372</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>170</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.90520302609233</v>
+        <v>-1.900930793898958</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.365576302119955</v>
+        <v>2.3651614082927</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.970707595523294</v>
+        <v>1.969544131465142</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3362548457778587</v>
+        <v>0.3370797408166339</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2021663692943108</v>
+        <v>-0.201258299785458</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.624687333127234</v>
+        <v>3.620870114211506</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.342399325321516</v>
+        <v>-2.337204345771617</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.812871628688129</v>
+        <v>-2.806293819517911</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5218952926513296</v>
+        <v>-0.517641433814731</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.159954786366967</v>
+        <v>2.161645145863226</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1880046785005476</v>
+        <v>0.1921859391927683</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.16657614836879</v>
+        <v>3.167745567126431</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.513518320972729</v>
+        <v>4.512196838534273</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.174118465559239</v>
+        <v>4.173682876693107</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>176</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.461107134335485</v>
+        <v>5.455120521341634</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.41771533955297</v>
+        <v>4.414012650571536</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.886482996592747</v>
+        <v>2.883590345718652</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.016736129200311</v>
+        <v>3.013632580830716</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.046496732309969</v>
+        <v>3.042619094269838</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.18484776093478</v>
+        <v>6.176045187065029</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.07738677093516</v>
+        <v>10.06474730058698</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.341165582011854</v>
+        <v>7.333786616841053</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>8.421290740700769</v>
+        <v>8.412839849607721</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.430819232579758</v>
+        <v>6.42635102821616</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.656580162771384</v>
+        <v>5.653415885716761</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.690223025902647</v>
+        <v>5.687799043062135</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.270391440223086</v>
+        <v>5.267544432117354</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.812713099190169</v>
+        <v>3.812720309848125</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>207</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.095933660466351</v>
+        <v>2.094036885418149</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.931098889695917</v>
+        <v>-1.924405727452772</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.292151171171739</v>
+        <v>-3.284675727068262</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.161898038564338</v>
+        <v>-3.154707937800154</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.130598620759734</v>
+        <v>1.12888380378304</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.953601953602011</v>
+        <v>-1.950510044857069</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.453794608072243</v>
+        <v>-4.444110165411566</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.993143713187351</v>
+        <v>-2.984078001003283</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.575355254331477</v>
+        <v>-2.566518955838035</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.460805197188584</v>
+        <v>-2.450460565986788</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.698306457844481</v>
+        <v>-1.689030315425093</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.664925397745442</v>
+        <v>-1.654647158079605</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.504527000214985</v>
+        <v>-4.490360706222631</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.319585756868022</v>
+        <v>-2.308272224187888</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8.390874217645901</v>
+        <v>-8.42815405305592</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.822960651123012</v>
+        <v>-2.843954934549892</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.269111409001653</v>
+        <v>-5.29650766467423</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.087576225111981</v>
+        <v>-3.105973571803283</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.651638465825272</v>
+        <v>-4.670454366422639</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.892658066571087</v>
+        <v>-5.916553689574414</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.387648194099867</v>
+        <v>-2.404514013998273</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.545300869981737</v>
+        <v>1.539995565835021</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.510938501984739</v>
+        <v>2.50843497613068</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.748971405442148</v>
+        <v>4.751093296257515</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.031931275296046</v>
+        <v>4.030876054413987</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.555508370763476</v>
+        <v>3.549795294233704</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.162418673388309</v>
+        <v>4.160468518340288</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.899112827861039</v>
+        <v>3.894725933090861</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.743849815383278</v>
+        <v>1.737281802364087</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.522106710893603</v>
+        <v>3.52203096774511</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.997294501472183</v>
+        <v>1.991437031322143</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4326323798423246</v>
+        <v>0.4209751486078588</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.060591095116884</v>
+        <v>-4.089611541438778</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.763149157401223</v>
+        <v>-3.792169603723117</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.366806390863253</v>
+        <v>2.364797394019917</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.360264013567992</v>
+        <v>-0.3802205297871524</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.09079673356973927</v>
+        <v>-0.1098874231195168</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.1533565508309</v>
+        <v>4.153623755488823</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.08108878446275</v>
+        <v>5.085234067535048</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.120556052057076</v>
+        <v>5.119617224880379</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.569722424506139</v>
+        <v>3.562998977571908</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.560827778694943</v>
+        <v>1.539993037120858</v>
       </c>
     </row>
     <row r="29">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.05598</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.07526538420606954</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.0156</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4044</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2380772159457436</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.02479</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3979~3992</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3979</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2389293021739007</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.06517</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3914~3927</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3914</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2143448646459376</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.1056</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3818~3831</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3818</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.3660564355845537</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.1459</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3704~3717</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3704</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.5698440237343263</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.1863</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3569~3582</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3569</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.6229748919575968</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.2267</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3419~3432</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3419</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.7160490428206998</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.2671</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3246~3258</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3246</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.835979756674071</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.3075</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3083~3095</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3083</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.8294641683521391</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.3479</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2900~2912</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2900</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.7420646938363404</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.3883</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2720~2731</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2720</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.4612156911363741</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.4286</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2559~2567</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2559</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.4092934039653287</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.469</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2381~2389</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2381</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3320116588607647</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.5094</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2234~2240</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2234</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5422759655043095</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.5498</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2086~2091</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2086</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.7825062039411463</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.5902</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1949~1953</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1949</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.013986154956434</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.6306</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1800~1804</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1800</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.8879364026281635</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.6709</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1636~1638</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1636</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.23061540384375</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.7113</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1466~1468</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1466</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.593755140280493</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.7517</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1290~1292</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1290</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.066933196817885</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.7921</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1083~1085</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1083</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.870616979329192</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.8325</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>889~890</t>
-        </is>
+      <c r="B28" t="n">
+        <v>889</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.899820106756323</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.8729</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>713~713</t>
-        </is>
+      <c r="B29" t="n">
+        <v>713</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.186786083717095</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.9133</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>546~546</t>
-        </is>
+      <c r="B30" t="n">
+        <v>546</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>3.001067174295521</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.9536</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>406~406</t>
-        </is>
+      <c r="B31" t="n">
+        <v>406</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>3.171586310331897</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.994</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>287~287</t>
-        </is>
+      <c r="B32" t="n">
+        <v>287</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.558826488152398</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1.034</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>194~194</t>
-        </is>
+      <c r="B33" t="n">
+        <v>194</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.5993451849446672</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1.075</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>121~121</t>
-        </is>
+      <c r="B34" t="n">
+        <v>121</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.225569944252832</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1.115</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.05598</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4.649418822647164</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.0156</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>121~121</t>
-        </is>
+      <c r="B7" t="n">
+        <v>121</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>8.663586473178448</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.02479</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>186~186</t>
-        </is>
+      <c r="B8" t="n">
+        <v>186</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.571077808822288</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.06517</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>251~251</t>
-        </is>
+      <c r="B9" t="n">
+        <v>251</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3.681860484570898</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.1056</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>347~347</t>
-        </is>
+      <c r="B10" t="n">
+        <v>347</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.278895973738145</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.1459</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>461~461</t>
-        </is>
+      <c r="B11" t="n">
+        <v>461</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>4.773372959616495</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.1863</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>596~596</t>
-        </is>
+      <c r="B12" t="n">
+        <v>596</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>3.88240060596452</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.2267</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>746~746</t>
-        </is>
+      <c r="B13" t="n">
+        <v>746</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3.40468500418681</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.2671</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>919~920</t>
-        </is>
+      <c r="B14" t="n">
+        <v>919</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>3.050039940659588</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.3075</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1082~1083</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1082</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.446543212569338</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.3479</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1265~1266</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1265</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.771964523391922</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.3883</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1445~1447</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1445</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.9274324468943789</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.4286</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1606~1611</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1606</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.7033338709756265</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.469</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1784~1789</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1784</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3972952235079106</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.5094</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1931~1938</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1931</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.5842535936877908</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.5498</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2079~2087</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2079</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.7445164227495127</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.5902</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2216~2225</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2216</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.8529888820077218</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.6306</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2365~2374</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2365</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.6400263572782166</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.6709</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2529~2540</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2529</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.7611548556430421</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.7113</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2699~2710</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2699</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.8329217150439234</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.7517</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2875~2886</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2875</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.4490862758579226</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.7921</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3082~3093</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3082</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.2787600143580491</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.8325</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3276~3288</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3276</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.7598616778742127</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.8729</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3452~3465</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3452</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.6319664587381126</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.9133</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3619~3632</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3619</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.4284603466416925</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.9536</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3759~3772</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3759</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.3195252767317172</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.994</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3878~3891</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3878</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1675580837668988</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1.034</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3971~3984</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3971</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.00849856117383041</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1.075</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4044</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.01623841880499555</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1.115</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.001987416448372414</v>

--- a/workspaces/btc_daily_14days/volatility/bb_pct_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_pct_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Pct-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Pct-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,157 +568,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03579</t>
+          <t>X ≈ -0.03578</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>37</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17.7196277929622</v>
+        <v>17.73212317215461</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0509168531243418</v>
+        <v>-0.03804611688357795</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.946248596740404</v>
+        <v>4.959222872754083</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.010665853087467</v>
+        <v>-2.997721394286664</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.844454116767579</v>
+        <v>1.857536210296118</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.5553103956289789</v>
+        <v>-0.542294196182425</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.756100359913411</v>
+        <v>4.769145432927857</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.591889431281317</v>
+        <v>1.605051028722315</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.167887567740912</v>
+        <v>-1.154705934682944</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.717573470638605</v>
+        <v>-4.704183081167976</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4781194778387317</v>
+        <v>0.4915665902129618</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.213954472255239</v>
+        <v>3.227400296835164</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.609544334653734</v>
+        <v>-2.595991892662823</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.360498363370546</v>
+        <v>-2.370927999068698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.004595</t>
+          <t>X ≈ 0.004605</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>65</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.185916429763239</v>
+        <v>-0.1734360214217219</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.461205380264936</v>
+        <v>-9.448342751836826</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.720362842147317</v>
+        <v>-3.707395323462919</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.547286591329645</v>
+        <v>2.560233615391461</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4753005512298429</v>
+        <v>0.4883811616022058</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.833510830078296</v>
+        <v>-3.820496974145648</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.383312433327312</v>
+        <v>-2.370271000854785</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.458971762391407</v>
+        <v>-7.445814070588405</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.912017087810071</v>
+        <v>-2.89883645274891</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8486775745972253</v>
+        <v>0.8620689608625156</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.6443083210169362</v>
+        <v>0.6577552056295559</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.754185382646497</v>
+        <v>3.767631119403163</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2587749825984957</v>
+        <v>0.2723275089663417</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.183783186655369</v>
+        <v>-7.194212822354224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.04498</t>
+          <t>X ≈ 0.04499</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>65</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.719290663473494</v>
+        <v>-1.706812936363988</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-6.392745936821974</v>
+        <v>-6.379882715045113</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.6517222722699003</v>
+        <v>-0.6387539556102553</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.125622041415511</v>
+        <v>-5.112681023579754</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.594605520024096</v>
+        <v>-2.581527698190477</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.83325012786807</v>
+        <v>-3.820237300725736</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.918883668378299</v>
+        <v>-3.905843795606643</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.314171858280375</v>
+        <v>-1.301012632436169</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.44838927221199</v>
+        <v>-4.435209770535167</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.762019958222204</v>
+        <v>-3.7486302237714</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.042120049538539</v>
+        <v>-7.028675010893735</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.547280680817721</v>
+        <v>-8.533836751056327</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.431568816250923</v>
+        <v>-7.418016908240837</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.183783186654672</v>
+        <v>-7.194212822352824</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>96</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.819350737892059</v>
+        <v>5.831833237075244</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.215778654401532</v>
+        <v>4.228648401998363</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.861324827057139</v>
+        <v>4.874295637157232</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.914774365086814</v>
+        <v>2.927719134024997</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.37788990631126</v>
+        <v>2.390969339624249</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.675889580519531</v>
+        <v>2.688904616977027</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.552159552382193</v>
+        <v>1.565200857089103</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.074133889757611</v>
+        <v>-3.06097632812633</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.09545246183518</v>
+        <v>-2.082273029398998</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.067131266731785</v>
+        <v>-6.053742855667366</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.232412118158706</v>
+        <v>-5.218967284528269</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.199488555851765</v>
+        <v>-5.186044568236646</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.662457864416496</v>
+        <v>-6.648906099458152</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-6.414552417425071</v>
+        <v>-6.424982053123223</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>114</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.255252568860442</v>
+        <v>6.267733545359732</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.275330820158999</v>
+        <v>7.288201162389775</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.38143004033674</v>
+        <v>10.39440341986923</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.015134502691865</v>
+        <v>7.028080419286091</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.229040842961695</v>
+        <v>1.242117838297766</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.974447347180238</v>
+        <v>-1.961436512542292</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.184039251323853</v>
+        <v>-1.171000712963533</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.650714357769935</v>
+        <v>-1.637557578932153</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.792017862881579</v>
+        <v>1.80519757002466</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.06696484092259425</v>
+        <v>0.08035399188727155</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.890575420257186</v>
+        <v>-1.87713062844638</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1033936453819777</v>
+        <v>-0.08994942953231089</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3532948459878256</v>
+        <v>0.3668468516523262</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.357377407136809</v>
+        <v>2.346947771439041</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.8347787072944115</v>
+        <v>1.189142234188282</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.183621894113315</v>
+        <v>2.516756921797061</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.959018321748424</v>
+        <v>7.25433485176103</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.614242982498439</v>
+        <v>5.920477200053355</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.817632054899732</v>
+        <v>6.118650685495197</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.116897070640746</v>
+        <v>6.417932353030565</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.076786160361813</v>
+        <v>3.39967326587778</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.090333374925606</v>
+        <v>4.402550813951237</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.811344275809383</v>
+        <v>2.139984283309353</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.257068950200846</v>
+        <v>-0.9118087844411065</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.498518573551827</v>
+        <v>1.822159785380862</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.013787086911563</v>
+        <v>3.326627308523165</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.594384039400943</v>
+        <v>2.907416127625517</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6224846196122655</v>
+        <v>0.9279591233476623</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.498495253382046</v>
+        <v>1.203358415330122</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5590554390363351</v>
+        <v>0.2686816194211232</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.486825551085261</v>
+        <v>3.218771529953386</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.624567593041689</v>
+        <v>1.343025893264752</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.747751264676268</v>
+        <v>3.484115057471364</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.716343105564981</v>
+        <v>2.443637423469255</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.628693304696128</v>
+        <v>4.369331992990034</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8362510471062166</v>
+        <v>0.5545985791623949</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1099479204685991</v>
+        <v>-0.1762328842192318</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.404897005879846</v>
+        <v>-1.695420309533432</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2777720287383261</v>
+        <v>-0.5593826587017716</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2436877806651481</v>
+        <v>-0.5253813785562329</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.663387547266957</v>
+        <v>-2.958474536162683</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.4145524174244528</v>
+        <v>-0.7202840665454175</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.53421163445131</v>
+        <v>1.237357024070349</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.386038667553329</v>
+        <v>-2.360040975457771</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.628470241523068</v>
+        <v>-1.610661568018436</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.382971911911397</v>
+        <v>1.384825673683352</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2670966914154889</v>
+        <v>0.2751485799478033</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.01247689874258384</v>
+        <v>-0.0001933037060624088</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.828484691924466</v>
+        <v>-1.80506768688614</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-4.030543245080587</v>
+        <v>-3.992344697707907</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.248199551270275</v>
+        <v>-5.2019952132976</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.260329026818304</v>
+        <v>-7.200238638250646</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.157883971238789</v>
+        <v>-5.110363266373376</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.280079298021995</v>
+        <v>-6.226518141735767</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.549613302822408</v>
+        <v>-5.499445293189154</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.547500394303221</v>
+        <v>-5.275556765766432</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>163</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.9592163137080902</v>
+        <v>-0.9466940240324675</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.328048911177639</v>
+        <v>2.340110505545681</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.736055274296064</v>
+        <v>-1.722798959663891</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3823714456253953</v>
+        <v>-0.3694982460374021</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3043139569715123</v>
+        <v>0.3170819054260292</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.6217778720451577</v>
+        <v>-0.6086217297526773</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.130638516796083</v>
+        <v>1.143293902758771</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05264674592490337</v>
+        <v>0.06588378189866972</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.89347476079223</v>
+        <v>4.90522284460922</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.8201559258247</v>
+        <v>2.832905631214423</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.776809366487285</v>
+        <v>0.790248060958028</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8111598061385834</v>
+        <v>0.8245649728712152</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.61793483925603</v>
+        <v>1.631227015248101</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.481153104047792</v>
+        <v>2.47072346834964</v>
       </c>
     </row>
     <row r="15">
@@ -1043,98 +1043,98 @@
         <v>183</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.214483163411245</v>
+        <v>-2.201960873735622</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.081284194574692</v>
+        <v>1.093673152354285</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1419100997227147</v>
+        <v>0.1545509049139042</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.996405261525176</v>
+        <v>3.008104772825085</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2643143177305092</v>
+        <v>-0.2513916768985283</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.124113867504285</v>
+        <v>1.13668310861911</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5959169773213944</v>
+        <v>-0.5827165638213927</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.061741866709532</v>
+        <v>-1.04811468144328</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.760331427277151</v>
+        <v>-2.746121422802688</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.42657444721538</v>
+        <v>-1.412440460052153</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.724078748785608</v>
+        <v>-2.709436315844876</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.42223760806484</v>
+        <v>-5.406690093569956</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.39104970598504</v>
+        <v>-6.375028234784523</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.409087936550158</v>
+        <v>-3.41951757224831</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.3681</t>
+          <t>X ≈ 0.368</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>180</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.98600517908023</v>
+        <v>-4.973482889404607</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.174796773828113</v>
+        <v>-2.161175986795023</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.677606453513853</v>
+        <v>-3.663506511849938</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.994175698129396</v>
+        <v>-2.980342985255831</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.318787788908018</v>
+        <v>-1.305393620945239</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.303778562335971</v>
+        <v>2.31596255535591</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5535564464475229</v>
+        <v>-0.540242559419525</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6394266468786967</v>
+        <v>0.6526022564807761</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.086718718074245</v>
+        <v>-1.072874609729517</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.388495653961066</v>
+        <v>-1.374162136548854</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.625783352280159</v>
+        <v>0.639470374181613</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.673602807222785</v>
+        <v>-2.658668199580525</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.335726250299238</v>
+        <v>3.027745661773871</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.363225360353169</v>
+        <v>1.352795724655017</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>161</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.286489808345671</v>
+        <v>-1.273967518670048</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.928305943166976</v>
+        <v>-2.914022470735965</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-8.563834471868454</v>
+        <v>-8.884399286039034</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.717052446749051</v>
+        <v>-4.702290543209195</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.642730413516169</v>
+        <v>-4.627857492073396</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3305666784620982</v>
+        <v>0.007485041198329156</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.85660845433965</v>
+        <v>-2.84234926311634</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.329435768168132</v>
+        <v>-3.314698167504154</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.634271592507652</v>
+        <v>-4.618942146820928</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.09363845160309836</v>
+        <v>0.1075321862181084</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.597005476791793</v>
+        <v>-2.582014110326853</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.585634045588286</v>
+        <v>-1.929649896321891</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.00588865653333</v>
+        <v>-1.992332610181727</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.3772853366794</v>
+        <v>-2.387714972377552</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>178</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-10.3252897780605</v>
+        <v>-10.31276748838488</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-11.93513022821162</v>
+        <v>-11.91730057193213</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.0884812703241</v>
+        <v>-10.07547413890649</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.282282110380876</v>
+        <v>-8.26605277718955</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.898568041248005</v>
+        <v>-4.883619298732199</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.238057103437384</v>
+        <v>-1.225014207143019</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.808904671110255</v>
+        <v>-5.793380673157024</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.471933021754047</v>
+        <v>-3.457058902188457</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.850437557216267</v>
+        <v>-1.836117969130242</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.824383943340294</v>
+        <v>-3.808925280360839</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.345818026438501</v>
+        <v>-2.330863077090065</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.558625880329018</v>
+        <v>-4.545173591608908</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.417082738464927</v>
+        <v>-4.403526692113324</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.85275466461561</v>
+        <v>-5.863184300313762</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>147</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.863433654347872</v>
+        <v>-2.85091136467225</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.644127561538355</v>
+        <v>3.656053243912666</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.604864968177637</v>
+        <v>4.617872099595239</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.027304548405539</v>
+        <v>2.039734745236458</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.858189515791949</v>
+        <v>1.499029626203928</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.479510890635396</v>
+        <v>1.492553786929761</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7106179096837337</v>
+        <v>0.7237545667240823</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.277630187499135</v>
+        <v>2.290351221424324</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8560677708962388</v>
+        <v>0.8695114683327247</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6828780538447887</v>
+        <v>-0.6683504154648503</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.2171778063055</v>
+        <v>-3.596690462960112</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.863066757803452</v>
+        <v>-3.849614469083342</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8819608245308288</v>
+        <v>-0.8684047781792259</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.353327927628683</v>
+        <v>-3.363757563326836</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>148</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.843671854625718</v>
+        <v>-2.831149564950096</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.463831179709807</v>
+        <v>-7.820208272122152</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.466006292985284</v>
+        <v>-2.452999161567682</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.709840817180627</v>
+        <v>-5.694141993633046</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.270896478338493</v>
+        <v>-8.257785673963554</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-10.67209633055863</v>
+        <v>-10.65905343426427</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.735965172618201</v>
+        <v>-8.718478313327388</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.156740790339953</v>
+        <v>-5.140708353082857</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.895842120853786</v>
+        <v>-5.879313387198415</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.425000323135187</v>
+        <v>-7.40727093605387</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.602726620425592</v>
+        <v>-5.589269326715375</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.244019138756144</v>
+        <v>-6.230566850036034</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.015625101052088</v>
+        <v>-8.002069054700485</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.792930795802832</v>
+        <v>-9.803360431500984</v>
       </c>
     </row>
     <row r="21">
@@ -1355,150 +1355,150 @@
         <v>137</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.510591785320123</v>
+        <v>-2.498069495644501</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4910235768966587</v>
+        <v>-0.4781137673206075</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.155957769089774</v>
+        <v>-0.1429506376721719</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.3532557274165953</v>
+        <v>-0.7399054374474971</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.294501091160441</v>
+        <v>1.307611895535381</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.591061058554544</v>
+        <v>1.60410395484891</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.237468346449809</v>
+        <v>2.249981544144909</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.688017097395537</v>
+        <v>4.699422433772142</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.39614054274778</v>
+        <v>-3.38040660821494</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.599196417039316</v>
+        <v>-0.5843354350702157</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.993730763254867</v>
+        <v>-2.980273469544649</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7695665840112937</v>
+        <v>-0.7561142952911837</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.459894187657099</v>
+        <v>-0.4463381413054961</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.670026869979516</v>
+        <v>-1.680456505677668</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.6104</t>
+          <t>X ≈ 0.6103</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>149</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.536734840801287</v>
+        <v>2.54925713047691</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.749022283186925</v>
+        <v>-1.736112473610874</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.475032896923764</v>
+        <v>-1.462025765506162</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.014886717590841</v>
+        <v>-2.001907575192376</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.55262673607303</v>
+        <v>-2.539515931698091</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.595512237671635</v>
+        <v>-3.582469341377269</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3396438935998773</v>
+        <v>0.353121420709094</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.479621914229398</v>
+        <v>-3.463968215924538</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8595435088726475</v>
+        <v>-0.8448148635176125</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.724655683193077</v>
+        <v>-3.707828108441788</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5737043095240821</v>
+        <v>-0.5602470158138644</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5393211521788075</v>
+        <v>-0.5258688634586974</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.301857642318495</v>
+        <v>-2.288301595966892</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.380995370444737</v>
+        <v>-1.391425006142889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.6508</t>
+          <t>X ≈ 0.6507</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>164</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.530495585107843</v>
+        <v>-2.51797329543222</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.341156778480283</v>
+        <v>-2.328246968904232</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.122153931288594</v>
+        <v>-2.109146799870992</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.772055141000898</v>
+        <v>-0.7590759986024338</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.730936590158436</v>
+        <v>1.744047394533375</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.839461676075445</v>
+        <v>-2.826418779781079</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7657962512382568</v>
+        <v>-1.093206827371326</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.284656723543158</v>
+        <v>-4.267827182848038</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.915063717146779</v>
+        <v>-1.89918320936598</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.195600191296172</v>
+        <v>-1.542089972975511</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4289147770691102</v>
+        <v>0.4423720707793279</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.365970358268392</v>
+        <v>-1.352518069548282</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.04304332346991657</v>
+        <v>0.05659936982151947</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9025207533070372</v>
+        <v>0.892091117608885</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>170</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.900930793898958</v>
+        <v>-1.888408504223335</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.3651614082927</v>
+        <v>2.378071217868751</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.969544131465142</v>
+        <v>1.982551262882744</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3370797408166339</v>
+        <v>0.3500588832150981</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.201258299785458</v>
+        <v>-0.1881474954105187</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.620870114211506</v>
+        <v>3.633913010505871</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.337204345771617</v>
+        <v>-2.324138091471141</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.806293819517911</v>
+        <v>-2.789875943736497</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.517641433814731</v>
+        <v>-0.502341293769895</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.161645145863226</v>
+        <v>2.175050273516057</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1921859391927683</v>
+        <v>0.205643232902986</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.167745567126431</v>
+        <v>3.181197855846541</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.512196838534273</v>
+        <v>4.525752884885875</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.173682876693107</v>
+        <v>4.163253240994955</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>176</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.455120521341634</v>
+        <v>5.467642811017257</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.414012650571536</v>
+        <v>4.426922460147587</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.883590345718652</v>
+        <v>2.896597477136254</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.013632580830716</v>
+        <v>3.02661172322918</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.042619094269838</v>
+        <v>3.055729898644778</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.176045187065029</v>
+        <v>6.189088083359394</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.06474730058698</v>
+        <v>10.07781355488746</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.333786616841053</v>
+        <v>7.343222972009436</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>8.412839849607721</v>
+        <v>8.421785693365685</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>6.439756155868992</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.653415885716761</v>
+        <v>5.666873179426979</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.687799043062135</v>
+        <v>5.701251331782245</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.267544432117354</v>
+        <v>5.281100478468957</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.812720309848125</v>
+        <v>3.802290674149972</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>207</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.094036885418149</v>
+        <v>2.106559175093771</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.924405727452772</v>
+        <v>-1.911495917876721</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.284675727068262</v>
+        <v>-3.271668595650659</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.154707937800154</v>
+        <v>-3.14172879540169</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.12888380378304</v>
+        <v>1.141994608157979</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.950510044857069</v>
+        <v>-1.937467148562703</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.444110165411566</v>
+        <v>-4.43104391111109</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.984078001003283</v>
+        <v>-2.96645393884198</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.566518955838035</v>
+        <v>-2.548947189621565</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.450460565986788</v>
+        <v>-2.437055438333957</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.689030315425093</v>
+        <v>-1.675573021714875</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.654647158079605</v>
+        <v>-1.641194869359495</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.490360706222631</v>
+        <v>-4.476804659871028</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.308272224187888</v>
+        <v>-2.31870185988604</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>194</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8.42815405305592</v>
+        <v>-8.415631763380297</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.843954934549892</v>
+        <v>-2.831045124973841</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.29650766467423</v>
+        <v>-5.283500533256628</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.105973571803283</v>
+        <v>-3.092994429404818</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.670454366422639</v>
+        <v>-4.6573435620477</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.916553689574414</v>
+        <v>-5.903510793280049</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.404514013998273</v>
+        <v>-2.391447759697797</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.539995565835021</v>
+        <v>1.25462569779765</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.50843497613068</v>
+        <v>2.52227486594267</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.751093296257515</v>
+        <v>4.764498423910347</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.030876054413987</v>
+        <v>4.044333348124205</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.549795294233704</v>
+        <v>3.563247582953814</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.160468518340288</v>
+        <v>4.174024564691891</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.894725933090861</v>
+        <v>3.884296297392709</v>
       </c>
     </row>
     <row r="28">
@@ -1719,150 +1719,150 @@
         <v>176</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.737281802364087</v>
+        <v>1.74980409203971</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.52203096774511</v>
+        <v>3.534940777321161</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.991437031322143</v>
+        <v>2.004444162739745</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4209751486078588</v>
+        <v>0.433954291006323</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.089611541438778</v>
+        <v>-4.076500737063839</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.792169603723117</v>
+        <v>-3.779126707428752</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.364797394019917</v>
+        <v>2.377863648320393</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3802205297871524</v>
+        <v>-0.3670395204919146</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.1098874231195168</v>
+        <v>-0.4286600835518612</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.153623755488823</v>
+        <v>4.167028883141654</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.085234067535048</v>
+        <v>5.098691361245265</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.119617224880379</v>
+        <v>5.133069513600489</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.562998977571908</v>
+        <v>3.576555023923511</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.539993037120858</v>
+        <v>1.529563401422706</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.8931</t>
+          <t>X ≈ 0.893</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>167</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.79398682949062</v>
+        <v>3.806509119166243</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.176425192574271</v>
+        <v>5.189335002150322</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.008862675698999567</v>
+        <v>0.004144455718602558</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.471423914348946</v>
+        <v>-3.458444771950482</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.213437943792407</v>
+        <v>-2.200327139417467</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.712403191705455</v>
+        <v>-3.69936029541109</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.797136908977734</v>
+        <v>-3.784070654677258</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.869110726920887</v>
+        <v>-1.855929717625649</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1337034274745079</v>
+        <v>-0.1205046885197447</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.181433402921563</v>
+        <v>-2.168028275268732</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.805430039227893</v>
+        <v>1.818887332938111</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.83382517262126</v>
+        <v>4.84727746134137</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.413570561676359</v>
+        <v>4.427126608027962</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.465687103533476</v>
+        <v>3.455257467835324</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.9335</t>
+          <t>X ≈ 0.9334</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>140</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.519083969465655</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5335833617457055</v>
+        <v>-0.5206735521696544</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.642976503086359</v>
+        <v>2.655983634503961</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.949094134907405</v>
+        <v>2.962204939282344</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.675107501194454</v>
+        <v>4.688150397488819</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.447516641065057</v>
+        <v>7.460582895365533</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.980333242283514</v>
+        <v>6.993514251578752</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.919333356101234</v>
+        <v>6.932532095055997</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.212065313930452</v>
+        <v>8.225470441583283</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.72159770389856</v>
+        <v>3.735054997608778</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.327409432672582</v>
+        <v>7.340861721392692</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.478583393156256</v>
+        <v>5.492139439507859</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.15687615400401</v>
+        <v>7.146446518305858</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>119</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.649418822647142</v>
+        <v>4.661941112322765</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.483312637540109</v>
+        <v>3.496319768957711</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.134574173508945</v>
+        <v>6.147553315907409</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.5541361517140899</v>
+        <v>0.5672469560890292</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.3725864927911</v>
+        <v>3.385629389085466</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.447516641065008</v>
+        <v>2.460582895365484</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.501341645644899</v>
+        <v>4.514522654940137</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.919333356101248</v>
+        <v>1.932532095056011</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.270888843342235</v>
+        <v>5.284293970995066</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.545127115663334</v>
+        <v>2.558584409373552</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.05850186964735116</v>
+        <v>0.07195415836746122</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.839927930971378</v>
+        <v>3.853483977322981</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.408976994340087</v>
+        <v>2.398547358641935</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.646346626026606</v>
+        <v>7.301692665117855</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.808966561449417</v>
+        <v>2.4296370068366</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.715173123670041</v>
+        <v>5.295735187298952</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.770157439073216</v>
+        <v>4.339003809148167</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.144607862020422</v>
+        <v>-0.5471118309040364</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.303371710103818</v>
+        <v>0.8372187204701902</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1433691756272424</v>
+        <v>-0.3344481605351177</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.12779868007155</v>
+        <v>5.720222326112939</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.991529976684916</v>
+        <v>4.572283647850988</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.234939294364537</v>
+        <v>-1.712417757174521</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.936651467339424</v>
+        <v>3.517663693260936</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.046303441889222</v>
+        <v>4.638998367355455</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.701317648148574</v>
+        <v>5.305804035781144</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>7.026307797629151</v>
+        <v>6.618496207746816</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.4386437996620316</v>
+        <v>-1.129564679183005</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-3.420080426324915</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.814949132921527</v>
+        <v>-3.13552215700188</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.794756054480537</v>
+        <v>2.400108391991921</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>1.256334839408325</v>
+        <v>0.5104674875448509</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1839137634253589</v>
+        <v>0.8078415171799165</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.09918004615308007</v>
+        <v>0.7231311579137483</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.107729380025681</v>
+        <v>-2.446640188575685</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.9408597748879046</v>
+        <v>1.546431708955581</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.09073458986001981</v>
+        <v>0.6965129126257494</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.255844279241032</v>
+        <v>1.843163105716904</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.07963557711219238</v>
+        <v>0.5261899067208518</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.869753201755685</v>
+        <v>-1.245312297943883</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.859420185315109</v>
+        <v>4.38582875768801</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>37</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.573138023519704</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>18.86796103979876</v>
+        <v>18.88087084937482</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.06768692779677</v>
+        <v>13.08069405921437</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.387129249593457</v>
+        <v>2.400108391991921</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.254113439926691</v>
+        <v>7.26722424430163</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.848852674939664</v>
+        <v>4.861895571234029</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.764118957667385</v>
+        <v>4.777185211967861</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.296935558885885</v>
+        <v>4.310116568181122</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.533232970000888</v>
+        <v>1.546431708955652</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.088513190378322</v>
+        <v>6.101918318031153</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4783544606553392</v>
+        <v>0.4918117543655569</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.620845726108939</v>
+        <v>8.634298014829049</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.497888412461272</v>
+        <v>5.511444458812875</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.85571785284567</v>
+        <v>13.84528821714752</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Pct-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Pct-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,209 +2210,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.05598</t>
+          <t>X &gt; -0.05597</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07526538420606954</v>
+        <v>-0.07554362516194146</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03709109271491684</v>
+        <v>-0.03738790767243216</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.04525451510145473</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06694056910164647</v>
+        <v>0.06661654237101544</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.06697292761445794</v>
+        <v>-0.06726742164935473</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.07268986502773345</v>
+        <v>0.07236276214128878</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1236418856834263</v>
+        <v>0.1233016879449025</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01242104682057033</v>
+        <v>0.01210524962181836</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1117674516190306</v>
+        <v>0.1114268484552738</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.05854197068862277</v>
+        <v>0.0582094108861213</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1613626402355024</v>
+        <v>0.1610035900200586</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2095689092479347</v>
+        <v>0.2091980863010434</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1216155202648181</v>
+        <v>0.1212636828863296</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.09120597512624329</v>
+        <v>0.09143146966019344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.0156</t>
+          <t>X &gt; -0.01559</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2380772159457436</v>
+        <v>-0.2384320482770832</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.03696459589612999</v>
+        <v>-0.03738188697013101</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0007358830405195249</v>
+        <v>0.0003059788262618213</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.09509868918596709</v>
+        <v>0.09464633313896087</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08446125616098499</v>
+        <v>-0.08487378367210141</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.07843566365391297</v>
+        <v>0.07798508784164682</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.08125786898053633</v>
+        <v>0.08080571302169659</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.002030073413116895</v>
+        <v>-0.002465577034982402</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1234754723204006</v>
+        <v>0.1230082855321868</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1022403562794025</v>
+        <v>0.1017714682918083</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1584645188232159</v>
+        <v>0.1579798987945651</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1820807129494</v>
+        <v>0.1815903034111201</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1466038769987392</v>
+        <v>0.1461186782621837</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1136374935546272</v>
+        <v>0.1139549060861427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.02479</t>
+          <t>X &gt; 0.0248</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3979</v>
+        <v>3980</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2389293021739007</v>
+        <v>-0.2394935411779855</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1169875656982313</v>
+        <v>0.1163147100691546</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.06152286900110937</v>
+        <v>0.06085888954204677</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.0550403293871895</v>
+        <v>0.05437920415744912</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09360539224552156</v>
+        <v>-0.09423598755220297</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1423402934836773</v>
+        <v>0.1416537647334053</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.121518504730723</v>
+        <v>0.1208358603588806</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1197847568918817</v>
+        <v>0.1190966471059767</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1730625586256167</v>
+        <v>0.1723600212076377</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.09004673496986015</v>
+        <v>0.08935454944328569</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1505278897348461</v>
+        <v>0.1498177392608255</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1237276585311236</v>
+        <v>0.1230243101851158</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1447714764297601</v>
+        <v>0.1440574787657596</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2328464265060362</v>
+        <v>0.2333094041636841</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.06517</t>
+          <t>X &gt; 0.06518</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3914</v>
+        <v>3915</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2143448646459376</v>
+        <v>-0.2151319164814041</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2250950459393692</v>
+        <v>0.2241698397326033</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07336776787249022</v>
+        <v>0.07247442847815933</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1410758567510513</v>
+        <v>0.1401669218593398</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.05207115404787999</v>
+        <v>-0.05293995659653206</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2083631287897063</v>
+        <v>0.2074322881701463</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1886176721431099</v>
+        <v>0.1876900564349313</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1435985484059756</v>
+        <v>0.1426744512362959</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2498112476916532</v>
+        <v>0.248858625668241</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1540182053473487</v>
+        <v>0.1530758802884904</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2699765652720885</v>
+        <v>0.2690008883693906</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2677275415300144</v>
+        <v>0.2667525270384203</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2705921506822548</v>
+        <v>0.2696091607977991</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3560147772611373</v>
+        <v>0.3566271422795424</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3818</v>
+        <v>3819</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3660564355845537</v>
+        <v>-0.3671373248976053</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1247530798805982</v>
+        <v>0.1235073778374769</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.04702088526573078</v>
+        <v>-0.04823121070308645</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.07133383034973662</v>
+        <v>0.07009491024167147</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.113170227330869</v>
+        <v>-0.1143736545376655</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1463195092595768</v>
+        <v>0.1450543506038997</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1543327008222732</v>
+        <v>0.1530629192621618</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.224505388129316</v>
+        <v>0.2232061283294726</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3087806861711044</v>
+        <v>0.3074573789770909</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3104431265939738</v>
+        <v>0.3090996034232703</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4083289260917269</v>
+        <v>0.4069545266511909</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4051955209298796</v>
+        <v>0.4038220533925454</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.444917137966037</v>
+        <v>0.4435231343470463</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.5262542876565917</v>
+        <v>0.5270996436565127</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3704</v>
+        <v>3705</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.5698440237343263</v>
+        <v>-0.571287197828596</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.09532409679103182</v>
+        <v>-0.09694473861028996</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3679829277923616</v>
+        <v>-0.3695430454899338</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1423792572979465</v>
+        <v>-0.1439969515750832</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1544801792783161</v>
+        <v>-0.15611185431721</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.211591491342233</v>
+        <v>0.2098694540853288</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1955244941658592</v>
+        <v>0.1938033387152629</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2822200347363619</v>
+        <v>0.2804603962452106</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2631302979030252</v>
+        <v>0.2613730654063957</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3179367887339666</v>
+        <v>0.3161379299320828</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4790835415031083</v>
+        <v>0.4772340698849575</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4208486432191805</v>
+        <v>0.4190150220979234</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4477370465204373</v>
+        <v>0.4458824045837986</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4698968266358747</v>
+        <v>0.4711043166478248</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3569</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6229748919575968</v>
+        <v>-0.638369966882756</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1815268731351338</v>
+        <v>-0.1965422241287555</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6451320364188717</v>
+        <v>-0.6600578658951193</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3601276468671486</v>
+        <v>-0.3750892700456561</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.380379633359027</v>
+        <v>-0.3952174036067859</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.01178095281728275</v>
+        <v>-0.02669444455758452</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.08653869283875792</v>
+        <v>0.07164074132268894</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1381754001256823</v>
+        <v>0.1233843814489006</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2045679871668611</v>
+        <v>0.1897868716168674</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3775125171610298</v>
+        <v>0.3629299593954443</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4405226759030612</v>
+        <v>0.4259844488965996</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3227688758057567</v>
+        <v>0.3082178041226271</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3665385752290788</v>
+        <v>0.3520834170988891</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4641250832758814</v>
+        <v>0.4536954475777293</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3419</v>
+        <v>3420</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7160490428206998</v>
+        <v>-0.7186090104353084</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2140180538387639</v>
+        <v>-0.2168107483068056</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.826411252015717</v>
+        <v>-0.8290478015622043</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4472011437920784</v>
+        <v>-0.4499428254062536</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5614909626088931</v>
+        <v>-0.5642292564432267</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1314705137290488</v>
+        <v>-0.1343200142464696</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1127368824109141</v>
+        <v>-0.1155978541446885</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1075490921271154</v>
+        <v>0.104597564063134</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2087192038982906</v>
+        <v>0.2057333463594375</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4557112385579671</v>
+        <v>0.4526066231587151</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4720360440505331</v>
+        <v>0.4689141854557093</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3476207326266518</v>
+        <v>0.3445354293329146</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4994689403575947</v>
+        <v>0.4963153279281158</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.502674842007977</v>
+        <v>0.5048425082807526</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3246</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.835979756674071</v>
+        <v>-0.8234574669984482</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.09825725095132753</v>
+        <v>-0.1019241002709848</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.7836644235546046</v>
+        <v>-0.787149836262337</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5447427145365964</v>
+        <v>-0.548294556411058</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6056516724506125</v>
+        <v>-0.6092236321462678</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1378124408370809</v>
+        <v>-0.1415098009482705</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.02129376132469929</v>
+        <v>-0.02503477623433525</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.328094370727527</v>
+        <v>0.3242118442689872</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4995531363210048</v>
+        <v>0.4956115870804183</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.8669481350182551</v>
+        <v>0.8628330789459113</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7720903147360119</v>
+        <v>0.7679882078273295</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7008530509575905</v>
+        <v>0.6967730514419586</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8218630340329298</v>
+        <v>0.8177146957883821</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8251271882439113</v>
+        <v>0.8146975525457592</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3083</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8294641683521391</v>
+        <v>-0.8169418786765164</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.226537466464471</v>
+        <v>-0.2310358877338814</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7333109663146331</v>
+        <v>-0.7376815238671171</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5533273777972241</v>
+        <v>-0.5577476211502486</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6537620836072122</v>
+        <v>-0.658197943733775</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1122249074971791</v>
+        <v>-0.1168133220656458</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.0821970896846338</v>
+        <v>-0.08680499182820256</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.342657446576645</v>
+        <v>0.337869798912628</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2672439489097798</v>
+        <v>0.2624728796599882</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7636809050794113</v>
+        <v>0.7586741992768324</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7718408157300232</v>
+        <v>0.7668113164681571</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6950210687667067</v>
+        <v>0.6900166183595786</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.77977425548886</v>
+        <v>0.7747038271306081</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7375721365812353</v>
+        <v>0.7271425008830832</v>
       </c>
     </row>
     <row r="16">
@@ -2737,98 +2737,98 @@
         <v>2900</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7420646938363404</v>
+        <v>-0.7295424041607177</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.3090655230059056</v>
+        <v>-0.3146295961256556</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7885404335852542</v>
+        <v>-0.7939844667867462</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7773277477958445</v>
+        <v>-0.7827652032528292</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6783375805573613</v>
+        <v>-0.6838688219513074</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1902421474369262</v>
+        <v>-0.1959132692433414</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.04977959332686765</v>
+        <v>-0.05551126159551956</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4312798860012563</v>
+        <v>0.4253301988799123</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4582943950622678</v>
+        <v>0.4523255546084854</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9018935704138826</v>
+        <v>0.895679020882767</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9924453951459995</v>
+        <v>0.986174529127922</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.081041185270209</v>
+        <v>1.07473983500892</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.232277974437046</v>
+        <v>1.225876574485937</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9992406860236684</v>
+        <v>0.9888110503255163</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.3883</t>
+          <t>X &gt; 0.3882</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2720</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4612156911363741</v>
+        <v>-0.4486934014607513</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1855980137603126</v>
+        <v>-0.1924316732137044</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5973522410899861</v>
+        <v>-0.6040896255693369</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6306245746120069</v>
+        <v>-0.6373372617967448</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.635954846181221</v>
+        <v>-0.6427385043708185</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3552876355836645</v>
+        <v>-0.3621403458712322</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.01644141922329823</v>
+        <v>-0.02343345512186801</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.4175054680020125</v>
+        <v>0.4102901362445621</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5605379099021803</v>
+        <v>0.5532579184249826</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.053463445556346</v>
+        <v>1.045889097477513</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.016709795041542</v>
+        <v>1.009118186440539</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.329510273008715</v>
+        <v>1.321803602003811</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.093079191475574</v>
+        <v>1.106635237827177</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9751534649283329</v>
+        <v>0.9647238292301807</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2559</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4092934039653287</v>
+        <v>-0.3967711142897059</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.01303999241039122</v>
+        <v>-0.02120224046611696</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.09613940828212009</v>
+        <v>-0.08313227686451796</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3735261426409053</v>
+        <v>-0.3815899080228462</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3838677549967997</v>
+        <v>-0.3920139412523653</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3984382977803662</v>
+        <v>-0.3853954014860008</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1622482613760567</v>
+        <v>0.1539192002462784</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6532450299494101</v>
+        <v>0.6446485250306324</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8873703952042575</v>
+        <v>0.8786679264377213</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.11385102821616</v>
+        <v>1.104926011394177</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.244067418630898</v>
+        <v>1.235054997608792</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.512917164487469</v>
+        <v>1.526369453207579</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.288051377301848</v>
+        <v>1.301607423653451</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.186072826811426</v>
+        <v>1.175643191113274</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2381</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3320116588607647</v>
+        <v>0.3445339485363874</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8782376480653014</v>
+        <v>0.8681322841037868</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6508731290733962</v>
+        <v>0.6638802604909984</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2177206285719109</v>
+        <v>0.2078407474629529</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.04635551184152575</v>
+        <v>-0.05622824044120023</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3356696512423767</v>
+        <v>-0.3226267549480113</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6086427267194239</v>
+        <v>0.5985304465569783</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9616371732518942</v>
+        <v>0.9512860395392337</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.092044824238634</v>
+        <v>1.081621260923676</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.483026091188457</v>
+        <v>1.472278186922281</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.512441887014923</v>
+        <v>1.501637701219209</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.966816644528343</v>
+        <v>1.980268933248453</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.714558673650643</v>
+        <v>1.728114720002246</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.712285045826135</v>
+        <v>1.701855410127983</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2234</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5422759655043095</v>
+        <v>0.5547982551799322</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6962386251107233</v>
+        <v>0.6846835906875341</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3906955102961689</v>
+        <v>0.403702641713771</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.09864773859181497</v>
+        <v>0.08729982639190581</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1716769617350451</v>
+        <v>-0.1585661573601058</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4551108059675499</v>
+        <v>-0.4420679096731845</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6019326318690403</v>
+        <v>0.5902905424994316</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8750431835050989</v>
+        <v>0.8631738722442037</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.107572410112098</v>
+        <v>1.095578351125511</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.625545298583212</v>
+        <v>1.613134231931632</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.823656790738333</v>
+        <v>1.837114084448551</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.350430279328158</v>
+        <v>2.363882568048268</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.88541291099741</v>
+        <v>1.898968957349012</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.045608728501989</v>
+        <v>2.035179092803837</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>2086</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7825062039411463</v>
+        <v>0.7950284936167691</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.275188927657908</v>
+        <v>1.288098737233959</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.5933761751502686</v>
+        <v>0.6063833065678708</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5107552679562986</v>
+        <v>0.4974884118970309</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4029560624535051</v>
+        <v>0.4160668668284444</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2697759905997898</v>
+        <v>0.2828188868941552</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.264448871113586</v>
+        <v>1.250740106575357</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.302993340805706</v>
+        <v>1.289144423226176</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.604458963603449</v>
+        <v>1.590441235723759</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.26767413463994</v>
+        <v>2.253124627359171</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.350552641578346</v>
+        <v>2.364009935288564</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.960199461435764</v>
+        <v>2.973651750155874</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.587883489033523</v>
+        <v>2.601439535385126</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.885543459852478</v>
+        <v>2.875113824154326</v>
       </c>
     </row>
     <row r="22">
@@ -3049,98 +3049,98 @@
         <v>1949</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.013986154956434</v>
+        <v>1.026508444632057</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.399340345371598</v>
+        <v>1.41225015494765</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6460486997069097</v>
+        <v>0.6590558311245118</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5714887242754898</v>
+        <v>0.584467866673954</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3402871712616857</v>
+        <v>0.353397975636625</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1768996158897949</v>
+        <v>0.1899425121841603</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.196052940830839</v>
+        <v>1.180500970122289</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.065051701681639</v>
+        <v>1.049427600524901</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.955963392731263</v>
+        <v>1.939854347380809</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.469193511540944</v>
+        <v>2.45257666868951</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.726215456592271</v>
+        <v>2.739672750302489</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.222373883306602</v>
+        <v>3.235826172026712</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.802119272361701</v>
+        <v>2.815675318713303</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.205765694427633</v>
+        <v>3.195336058729481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.6306</t>
+          <t>X &gt; 0.6305</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1800</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8879364026281635</v>
+        <v>0.9004586923037863</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.659954807402265</v>
+        <v>1.672864616978316</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8216271207613275</v>
+        <v>0.8346342521789296</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7855831358521925</v>
+        <v>0.7985622782506567</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5797561558132927</v>
+        <v>0.5928669601882319</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4891714859901484</v>
+        <v>0.5022143822845138</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.266944578629406</v>
+        <v>1.248989610601491</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.44124968433205</v>
+        <v>1.4230364764421</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.189024797364027</v>
+        <v>2.170363076505176</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.98190658377171</v>
+        <v>2.962521286352057</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.999375481676353</v>
+        <v>3.01283277538657</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.533758639021784</v>
+        <v>3.547210927741894</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.224615139188003</v>
+        <v>3.238171185539606</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1636</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.23061540384375</v>
+        <v>1.243137693519373</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.061044232881933</v>
+        <v>2.073954042457984</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.116724976834796</v>
+        <v>1.129732108252398</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9417278041919914</v>
+        <v>0.9547069465904556</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4643566501698828</v>
+        <v>0.4774674545448221</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8228486489356044</v>
+        <v>0.8358915452299698</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.470715664264056</v>
+        <v>1.483781918564532</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.015240302236414</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.600437093439687</v>
+        <v>2.578312704184192</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.400678656578016</v>
+        <v>3.414083784230847</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.257050026636975</v>
+        <v>3.270507320347193</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.024929516500741</v>
+        <v>4.038381805220851</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.543550211179301</v>
+        <v>3.557106257530904</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.854396237832127</v>
+        <v>3.843966602133975</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1466</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.593755140280493</v>
+        <v>1.606277429956116</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.025778257561456</v>
+        <v>2.038688067137507</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.017830531891299</v>
+        <v>1.030837663308901</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.011843882482452</v>
+        <v>1.024823024880916</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.5415425584184632</v>
+        <v>0.5546533627934025</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4983850410932433</v>
+        <v>0.5114279373876087</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.912288926000805</v>
+        <v>1.925355180301281</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.574354081703149</v>
+        <v>2.548204792645336</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.96201509455377</v>
+        <v>2.935550889485832</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.544359213755044</v>
+        <v>3.557764341407875</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.612457185481119</v>
+        <v>3.625914479191337</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.124330110902946</v>
+        <v>4.137782399623056</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.431224203914397</v>
+        <v>3.444780250266</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.817371184212504</v>
+        <v>3.806941548514352</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>1290</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.066933196817885</v>
+        <v>1.079455486493508</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.699941627197283</v>
+        <v>1.712851436773335</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7632772549660274</v>
+        <v>0.7762843863836295</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7387316259636165</v>
+        <v>0.7517107683620807</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2003104108914471</v>
+        <v>0.2134212152663864</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2762414594424385</v>
+        <v>-0.2631985631480731</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.8000155353595915</v>
+        <v>0.8130817896600675</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.925005146676583</v>
+        <v>1.894000761972407</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.218336678360366</v>
+        <v>2.187041334847954</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.151157229766547</v>
+        <v>3.164562357419378</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.334000804673771</v>
+        <v>3.347458098383989</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.911019620933942</v>
+        <v>3.924471909654052</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.180687490609188</v>
+        <v>3.194243536960791</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.818005722110286</v>
+        <v>3.807576086412134</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>1083</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.870616979329192</v>
+        <v>0.8831392690048148</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.392683919360323</v>
+        <v>2.405593728936374</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.536985719676181</v>
+        <v>1.549992851093783</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.482907055048663</v>
+        <v>1.495886197447128</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.0228268538013694</v>
+        <v>0.03593765817630867</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.04377109566450343</v>
+        <v>0.05681399195886883</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.802355350742445</v>
+        <v>1.815421605042921</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.863306357728966</v>
+        <v>2.823007339136375</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.132893572431527</v>
+        <v>3.09225797802911</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.221826559148759</v>
+        <v>4.23523168680159</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.294081545080481</v>
+        <v>4.307538838790698</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.974817426340969</v>
+        <v>4.98826971506108</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.646898918812504</v>
+        <v>4.660454965164107</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.988956354505227</v>
+        <v>4.978526718807075</v>
       </c>
     </row>
     <row r="28">
@@ -3361,150 +3361,150 @@
         <v>889</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.899820106756323</v>
+        <v>2.912342396431946</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.535437505028014</v>
+        <v>3.548347314604065</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.028209247869633</v>
+        <v>3.041216379287235</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.484305077106342</v>
+        <v>2.497284219504806</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.047007457539785</v>
+        <v>1.060118261914724</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.344449395255445</v>
+        <v>1.357492291549811</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.720389835286539</v>
+        <v>2.733456089587015</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.152082840999427</v>
+        <v>3.165263850294664</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.269164627192346</v>
+        <v>3.21664124433368</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.106328531028304</v>
+        <v>4.119733658681135</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.351518963741107</v>
+        <v>4.364976257451325</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.285789635147275</v>
+        <v>5.299241923867385</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.753049084944784</v>
+        <v>4.766605131296387</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.227742295736249</v>
+        <v>5.217312660038097</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.8729</t>
+          <t>X &gt; 0.8728</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>713</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.186786083717095</v>
+        <v>3.199308373392718</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.538746832604161</v>
+        <v>3.551656642180212</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.284130580425533</v>
+        <v>3.297137711843135</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.993626349779177</v>
+        <v>3.006605492177641</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.314952680289053</v>
+        <v>2.328063484663993</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.612394618004714</v>
+        <v>2.62543751429908</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.808165809568344</v>
+        <v>2.82123206386882</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.024011863802272</v>
+        <v>4.03719287309751</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.103264432037911</v>
+        <v>4.116463170992674</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.094653973517701</v>
+        <v>4.108059101170532</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.170405558036023</v>
+        <v>4.183862851746241</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.326808350725074</v>
+        <v>5.340260639445184</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.046806194198126</v>
+        <v>5.060362240549729</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.138042252982132</v>
+        <v>6.12761261728398</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.9133</t>
+          <t>X &gt; 0.9132</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>546</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.001067174295521</v>
+        <v>3.013589463971144</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.291328151437973</v>
+        <v>4.304335282855575</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.971031833496021</v>
+        <v>4.984010975894485</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.700009885823121</v>
+        <v>3.71312069019806</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.546902372989329</v>
+        <v>4.559945269283695</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.826487088437382</v>
+        <v>5.83966809773262</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.399186835954708</v>
+        <v>5.412385574909472</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.014263116128248</v>
+        <v>6.027668243781079</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.893758876059756</v>
+        <v>4.907216169769974</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.477592582855735</v>
+        <v>5.491044871575845</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.240488155061016</v>
+        <v>5.254044201412619</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.955410952538763</v>
+        <v>6.944981316840611</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>406</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.171586310331897</v>
+        <v>3.184108600007519</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.269372303278971</v>
+        <v>4.282282112855022</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.859725271559228</v>
+        <v>4.87273240297683</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.743672985447517</v>
+        <v>4.756652127845982</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.958946351656131</v>
+        <v>3.97205715603107</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.502693708091009</v>
+        <v>4.515736604385374</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.925349153380296</v>
+        <v>3.938415407680772</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.428609104352503</v>
+        <v>5.441790113647741</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.874998380731775</v>
+        <v>4.888197119686538</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.256400289299904</v>
+        <v>5.269805416952735</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.297952383701542</v>
+        <v>5.31140967741176</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.839724703608546</v>
+        <v>4.853176992328656</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.158386348821274</v>
+        <v>5.171942395172877</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.885940193412829</v>
+        <v>6.875510557714676</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>287</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.558826488152398</v>
+        <v>2.571348777828021</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.0831413769303</v>
+        <v>4.096051186506351</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.430432949079346</v>
+        <v>5.443440080496948</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.166957858690331</v>
+        <v>4.179937001088796</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.370696922363813</v>
+        <v>5.383807726738752</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.971274748581216</v>
+        <v>4.984317644875581</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.538108975559808</v>
+        <v>4.551175229860284</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.813085855523951</v>
+        <v>5.826266864819189</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.100518025090771</v>
+        <v>6.113716764045535</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.250392840062844</v>
+        <v>5.263797967715675</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.43936773874178</v>
+        <v>6.452825032451997</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.822182951836353</v>
+        <v>6.835635240556464</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.705064229393187</v>
+        <v>5.71862027574479</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.742242007662497</v>
+        <v>8.731812371964345</v>
       </c>
     </row>
     <row r="33">
@@ -3618,49 +3618,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.5993451849446672</v>
+        <v>0.3395967899784722</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.173338582289688</v>
+        <v>4.882256850760797</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.293933793218869</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.877795173249055</v>
+        <v>4.104890096773609</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.494013133434606</v>
+        <v>8.181985159062521</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.729599401047182</v>
+        <v>6.940897650236074</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.644865683774903</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.662218367467624</v>
+        <v>5.876298134362656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.632146316336872</v>
+        <v>6.840957003480902</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.359340718937815</v>
+        <v>8.555140771253605</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.639123477094451</v>
+        <v>7.837619100172901</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.673506634439882</v>
+        <v>7.871997252528224</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.706860270917666</v>
+        <v>5.913384860753276</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.56482902587436</v>
+        <v>9.728864100723392</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>121</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.225569944252832</v>
+        <v>1.238092233928455</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.35779798418114</v>
+        <v>10.37070779375719</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.7893755585763</v>
+        <v>10.8023826899939</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.134504724241637</v>
+        <v>5.147483866640101</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.86054631908682</v>
+        <v>12.87365712346176</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.67864941382729</v>
+        <v>10.69169231012165</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.59391569655501</v>
+        <v>10.60698195085548</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.95317857876524</v>
+        <v>10.96635958806048</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.06573241159121</v>
+        <v>10.07893115054597</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.34783863152195</v>
+        <v>13.36124375917478</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.4901927452209</v>
+        <v>11.50365003893111</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.35102218355807</v>
+        <v>12.36447447227818</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.27787501062969</v>
+        <v>10.2914310569813</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.00693518588119</v>
+        <v>12.99650555018304</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>15.33004651585973</v>
+        <v>15.34315732023467</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>13.24653607262303</v>
+        <v>13.2595789689174</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.16180235535075</v>
+        <v>13.17486860965123</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>13.88509514704544</v>
+        <v>13.89827615634068</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>13.82409526086314</v>
+        <v>13.8372939998179</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>16.54539864726378</v>
+        <v>16.55880377491661</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>16.3406453229462</v>
+        <v>16.35410261665642</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>13.99407609933924</v>
+        <v>14.00752838805935</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>12.38334529791816</v>
+        <v>12.39690134426976</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>12.63306663019445</v>
+        <v>12.6226369944963</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that BB Pct-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that BB Pct-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,209 +3904,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.05598</t>
+          <t>X &lt; -0.05597</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.661941112322786</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.465507444027736</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.187189373002603</v>
+        <v>8.200300177377542</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.257040450588846</v>
+        <v>1.270106704889322</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.640636742501869</v>
+        <v>4.6540418701547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3260213437204627</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-2.659138278607308</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.0156</t>
+          <t>X &lt; -0.01559</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>121</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8.663586473178448</v>
+        <v>8.676108762854071</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.399120298230727</v>
+        <v>5.412030107806778</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.524912748658927</v>
+        <v>2.537919880076529</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1758270382912173</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.248976071152931</v>
+        <v>6.262086875527871</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.587740322918187</v>
+        <v>1.600783219212552</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.32945288663764</v>
+        <v>2.342519140938116</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.341608330831349</v>
+        <v>4.354789340126587</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.9748233206821055</v>
+        <v>0.9880220596368687</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.777590697637642</v>
+        <v>1.790995825290473</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.08005518866340111</v>
+        <v>-0.06659789495318336</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.872118312309702</v>
+        <v>-0.858666023589592</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3605196387288601</v>
+        <v>0.374075685080463</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.6102409710051475</v>
+        <v>0.5998113353069954</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.02479</t>
+          <t>X &lt; 0.0248</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>186</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.571077808822288</v>
+        <v>5.583600098497911</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1960633356429682</v>
+        <v>0.2089731452190193</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3388290376485301</v>
+        <v>0.3518361690661322</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.006716578858182</v>
+        <v>1.019695721256646</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.231736224001068</v>
+        <v>4.244847028376007</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3095315157026306</v>
+        <v>-0.2964886194082652</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6810035842293942</v>
+        <v>0.6940698385298703</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2138201854478936</v>
+        <v>0.2270011947431314</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3848141093365598</v>
+        <v>-0.3716153703817966</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.453232748646272</v>
+        <v>1.466637876299103</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1732106071243962</v>
+        <v>0.1866679008346139</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.7452281730719719</v>
+        <v>0.7586804617920819</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3249735621270702</v>
+        <v>0.3385296084786731</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.113477148607402</v>
+        <v>-2.123906784305554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.06517</t>
+          <t>X &lt; 0.06518</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>251</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.681860484570898</v>
+        <v>3.69438277424652</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.515370498911288</v>
+        <v>-1.502460689335237</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.08179266700208387</v>
+        <v>0.094799798419686</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5847669493943997</v>
+        <v>-0.5717878069959355</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.462469206051367</v>
+        <v>2.475580010426306</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.224152601252904</v>
+        <v>-1.211109704958538</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.5120735695211991</v>
+        <v>-0.4990073152207231</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1824442192987163</v>
+        <v>-0.1692632100034785</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.438663228986989</v>
+        <v>-1.425464490032226</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1016498329970332</v>
+        <v>0.1150549606498643</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.696728989328513</v>
+        <v>-1.683271695618295</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.662345831983082</v>
+        <v>-1.648893543262972</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.684194068425995</v>
+        <v>-1.670638022074392</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.426504608659663</v>
+        <v>-3.436934244357815</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>347</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.278895973738145</v>
+        <v>4.291418263413767</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.07366241841077681</v>
+        <v>0.08657222798682795</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.407900340056273</v>
+        <v>1.420907471473875</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3854157205023796</v>
+        <v>0.3983948629008438</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.440654447793321</v>
+        <v>2.45376525216826</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1437479948944684</v>
+        <v>-0.130705098600103</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.05970272587359204</v>
+        <v>0.07276898017406808</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9838495489886014</v>
+        <v>-0.9706685396933636</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.621218311251596</v>
+        <v>-1.608019572296833</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.606790182158477</v>
+        <v>-1.593385054505646</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.676096820597103</v>
+        <v>-2.662639526886885</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.641713663251672</v>
+        <v>-2.628261374531562</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.061968274196573</v>
+        <v>-3.04841222784497</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.253169132122004</v>
+        <v>-4.263598767820156</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>461</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.773372959616495</v>
+        <v>4.785895249292118</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.860280908474365</v>
+        <v>1.873190718050417</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.634609598840889</v>
+        <v>3.647616730258491</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.029504813877892</v>
+        <v>2.042483956276357</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.141842817894656</v>
+        <v>2.154953622269595</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5975916001380597</v>
+        <v>-0.5845487038436943</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2484858380177073</v>
+        <v>-0.2354195837172313</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.149508716191839</v>
+        <v>-1.136327706896601</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7766691229815095</v>
+        <v>-0.7634703840267463</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.192954828616806</v>
+        <v>-1.179549700963975</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.482306851415956</v>
+        <v>-2.468849557705738</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.014084214677894</v>
+        <v>-2.000631925957784</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.217419085926487</v>
+        <v>-2.203863039574884</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.618456972739139</v>
+        <v>-2.628886608437291</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.88240060596452</v>
+        <v>3.967995192246221</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.935256523201609</v>
+        <v>2.021800723973001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.392736809893606</v>
+        <v>4.474600528497703</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.845137593507815</v>
+        <v>2.929783796039167</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.97785731803296</v>
+        <v>3.061510993362226</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.9263059671580152</v>
+        <v>1.013826396531655</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5060017800870824</v>
+        <v>0.5941076620561034</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.0388183813055818</v>
+        <v>0.1270390182693646</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1899667397760467</v>
+        <v>-0.1014473258580963</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.207877159703308</v>
+        <v>-1.118870309792655</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.580415718920207</v>
+        <v>-1.491075655657525</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.8748916219774614</v>
+        <v>-0.7866807528834485</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.127360998023043</v>
+        <v>-1.039327418592165</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.884351075142717</v>
+        <v>-1.818616893993777</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>746</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.40468500418681</v>
+        <v>3.417207293862432</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.659063133849898</v>
+        <v>1.671972943425949</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.21325608945169</v>
+        <v>4.226263220869292</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.6008818762147</v>
+        <v>2.613861018613164</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.134846720123761</v>
+        <v>3.1479575244987</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.287516539876954</v>
+        <v>1.300559436171319</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.33683107997733</v>
+        <v>1.349897334277806</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1994063943325628</v>
+        <v>0.2125874036278006</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1296900065950481</v>
+        <v>-0.1164912676402849</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.247911706368285</v>
+        <v>-1.234506578715454</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.318616773313209</v>
+        <v>-1.305159479602992</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7480405864771669</v>
+        <v>-0.7345882977570568</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.436391712167371</v>
+        <v>-1.422835665815768</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.588815152009047</v>
+        <v>-1.5992447877072</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.050039940659588</v>
+        <v>3.002254436349475</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.907897876401826</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.108815012403092</v>
+        <v>3.121822143820694</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.369502927619294</v>
+        <v>2.382482070017758</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.591951277764501</v>
+        <v>2.60506208213944</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.041567128523646</v>
+        <v>1.054610024818011</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7394421069035459</v>
+        <v>0.752508361204022</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.5973065092692664</v>
+        <v>-0.5841254999740286</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.093089004147217</v>
+        <v>-1.079890265192454</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.377996797870793</v>
+        <v>-2.364591670217962</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.039271861318809</v>
+        <v>-2.025814567608592</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.787497399625551</v>
+        <v>-1.77404511090544</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.207752010570452</v>
+        <v>-2.194195964218849</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.33403011056933</v>
+        <v>-2.294547270514059</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.446543212569338</v>
+        <v>2.408382862454573</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.111977909854389</v>
+        <v>1.12488771943044</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.379159064753651</v>
+        <v>2.392166196171253</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.955395576862529</v>
+        <v>1.968374719260993</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.247999292538282</v>
+        <v>2.261110096913221</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7910552653416687</v>
+        <v>0.8040981616360341</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7986576514858257</v>
+        <v>0.8117239057863017</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4995506780436045</v>
+        <v>-0.4863696687483667</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1912061505601628</v>
+        <v>-0.1780074116053996</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.595347956086698</v>
+        <v>-1.581942828433867</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.615429073571413</v>
+        <v>-1.601971779861195</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.39637370939311</v>
+        <v>-1.382921420673</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.63195611350514</v>
+        <v>-1.618400067153537</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.608637445151032</v>
+        <v>-1.577336623759876</v>
       </c>
     </row>
     <row r="16">
@@ -4428,101 +4428,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.771964523391922</v>
+        <v>1.74165697656904</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.108258209005861</v>
+        <v>1.121168018581912</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.056201508728385</v>
+        <v>2.069208640145987</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.107465699787703</v>
+        <v>2.120444842186167</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.885000250908263</v>
+        <v>1.898111055283202</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8396301823048091</v>
+        <v>0.8526730785991745</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.5969185819361726</v>
+        <v>0.6099848362366487</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5811652907789835</v>
+        <v>-0.5679842814837457</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5631762354130956</v>
+        <v>-0.5499774964583324</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.571279303537395</v>
+        <v>-1.557874175884564</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.776032627854974</v>
+        <v>-1.762575334144756</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.97861629515409</v>
+        <v>-1.96516400643398</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.31988196455081</v>
+        <v>-2.306325918199207</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-1.843623443328127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.3883</t>
+          <t>X &lt; 0.3882</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9274324468943789</v>
+        <v>0.9030618700181279</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6980288408409692</v>
+        <v>0.7109386504170203</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.33978763942752</v>
+        <v>1.352794770845122</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.47004077203502</v>
+        <v>1.483019914433484</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.484487559727185</v>
+        <v>1.497598364102124</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.021735993641883</v>
+        <v>1.034778889936248</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4532427739508051</v>
+        <v>0.4663090282512812</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4285916269039518</v>
+        <v>-0.415410617608714</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.6278085137773388</v>
+        <v>-0.6146097748225756</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.547042199150802</v>
+        <v>-1.533637071497971</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.475361522086217</v>
+        <v>-1.461904228376</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.062954867850664</v>
+        <v>-2.049502579130554</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.615864344445008</v>
+        <v>-1.64035142829745</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.466455531611459</v>
+        <v>-1.445728941089556</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7033338709756265</v>
+        <v>0.68285568162446</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3332251866271392</v>
+        <v>0.3461349962031903</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3448398571235813</v>
+        <v>0.3238030900328752</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8477637971845056</v>
+        <v>0.8607429395829698</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.8683487932924621</v>
+        <v>0.8814595976674013</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9518543714776797</v>
+        <v>0.930386422333541</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1213158064738877</v>
+        <v>0.1343820607743638</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7187700161733659</v>
+        <v>-0.7055890068781281</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.028371518266169</v>
+        <v>-1.015172779311406</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.381293471473086</v>
+        <v>-1.367888343820255</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.586046795790665</v>
+        <v>-1.572589502080447</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.015163417362956</v>
+        <v>-2.035414581546135</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.65493958666417</v>
+        <v>-1.675593325239831</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.557765368856735</v>
+        <v>-1.540103397242234</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3972952235079106</v>
+        <v>-0.4138769243891005</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.890925851564397</v>
+        <v>-0.8780160419883458</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6967486487193639</v>
+        <v>-0.7138159342894994</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.06313981141388325</v>
+        <v>-0.05016066901541905</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.2932935596437005</v>
+        <v>0.3064043640186398</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7335454258886713</v>
+        <v>0.7156352169199494</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4703824715738705</v>
+        <v>-0.4573162172733944</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9935255793648849</v>
+        <v>-0.9803445700696471</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.110485174556693</v>
+        <v>-1.09728643560193</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.624852105527538</v>
+        <v>-1.611446977874706</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.661726302816582</v>
+        <v>-1.648269009106365</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.268655196986671</v>
+        <v>-2.2854073648652</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.930380192277916</v>
+        <v>-1.947470222946151</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.986301296348373</v>
+        <v>-1.971200540517714</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5842535936877908</v>
+        <v>-0.5985024152687544</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5446404161463718</v>
+        <v>-0.5317306065703207</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2923432107568829</v>
+        <v>-0.307306944885724</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.09604105246496886</v>
+        <v>0.1090201948634331</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4121992116487974</v>
+        <v>0.3967502597336718</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7899100113457962</v>
+        <v>0.7743369382208201</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3800950237559348</v>
+        <v>-0.3670287694554588</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7439192494108156</v>
+        <v>-0.7307382401155778</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.959957895283047</v>
+        <v>-0.9467591563282838</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.551685147494432</v>
+        <v>-1.538280019841601</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.77995348534651</v>
+        <v>-1.794660764665103</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.389906360690802</v>
+        <v>-2.404300045485719</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.850609153427598</v>
+        <v>-1.865409891657613</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.09036805698959</v>
+        <v>-2.077155966166238</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7445164227495127</v>
+        <v>-0.7567780994998685</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.036939066443644</v>
+        <v>-1.049457178701203</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.4471228460058398</v>
+        <v>-0.4600278707693235</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.31686971339834</v>
+        <v>-0.3038905709998758</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.2055535206999863</v>
+        <v>-0.218678925054796</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.02587322715064744</v>
+        <v>-0.03902262143083846</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.974745206544867</v>
+        <v>-0.9616789522443909</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.057867155494392</v>
+        <v>-1.044686146199155</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.310897766592689</v>
+        <v>-1.297699027637925</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.968992226704621</v>
+        <v>-1.95558709905179</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.051697204843009</v>
+        <v>-2.064272894853993</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.664009527991929</v>
+        <v>-2.676292114204948</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.289273749700897</v>
+        <v>-2.30184696812583</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.638698641570826</v>
+        <v>-2.626905130045834</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8529888820077218</v>
+        <v>-0.8636653566799097</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.002493947562726</v>
+        <v>-1.01345043820492</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4288055160641164</v>
+        <v>-0.4401109184251624</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3192224666592764</v>
+        <v>-0.3305574965687299</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1129113967064512</v>
+        <v>-0.1244608701557866</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.07407790016485194</v>
+        <v>0.06249914644360643</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.7764215828731835</v>
+        <v>-0.7633553285727075</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.7030644411141509</v>
+        <v>-0.6898834318189131</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.439740002972137</v>
+        <v>-1.426541264017374</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.884459782594647</v>
+        <v>-1.871054654941815</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.109857906736835</v>
+        <v>-2.120800858247051</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.546994792498097</v>
+        <v>-2.55774125292006</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.176226839461826</v>
+        <v>-2.187237090184269</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.578812345222438</v>
+        <v>-2.568419130254007</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.6306</t>
+          <t>X &lt; 0.6305</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6400263572782166</v>
+        <v>-0.649337083165932</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.049807550536222</v>
+        <v>-1.059246184255301</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4948216178483946</v>
+        <v>-0.5045726233974719</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4261437450376349</v>
+        <v>-0.4359063748828973</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2666985112650266</v>
+        <v>-0.2766334049967867</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1572509381711598</v>
+        <v>-0.1671841413900239</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7063155967688886</v>
+        <v>-0.6932493424684125</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.8780156692523704</v>
+        <v>-0.8648346599571326</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.403346496760136</v>
+        <v>-1.390147757805373</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.00020025924691</v>
+        <v>-1.986795131594079</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.013199593398724</v>
+        <v>-2.022648674826826</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.420613984552361</v>
+        <v>-2.429891174360201</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.184138500334868</v>
+        <v>-2.193598987675443</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.503347343428828</v>
+        <v>-2.494297353207287</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7611548556430421</v>
+        <v>-0.7689915913371905</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.131400275041109</v>
+        <v>-1.139346218086374</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5991714199126648</v>
+        <v>-0.607393398073576</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.447672442125878</v>
+        <v>-0.4559391449067007</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.13675534684117</v>
+        <v>-0.1452335426142</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3305278890563201</v>
+        <v>-0.3388888093611158</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.7095472894795591</v>
+        <v>-0.71777720607151</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.097804089997446</v>
+        <v>-1.084623080702208</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.435047070102399</v>
+        <v>-1.421848331147636</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.948106137200341</v>
+        <v>-1.956060734423041</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.855021569403149</v>
+        <v>-1.863050016208803</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.35227674444544</v>
+        <v>-2.360108714174899</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.039767820847139</v>
+        <v>-2.047793957794163</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.282484406353035</v>
+        <v>-2.274784424664254</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8329217150439234</v>
+        <v>-0.8394553149312571</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9119517633698777</v>
+        <v>-0.9186703892808339</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4378422350440943</v>
+        <v>-0.4447915592945222</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3984416926084648</v>
+        <v>-0.4053928256215755</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1408646867587677</v>
+        <v>-0.1479855720903274</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.0819561375697333</v>
+        <v>-0.08906425777461635</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8122044071175551</v>
+        <v>-0.8190579813178829</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.205423308857632</v>
+        <v>-1.192242299562395</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.689631213737229</v>
+        <v>-1.696338518687227</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.726218728373809</v>
+        <v>-1.732943522553981</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.004848461229152</v>
+        <v>-2.011469884824919</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.627236712663851</v>
+        <v>-1.634057207236744</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.875834373704713</v>
+        <v>-1.869426497567197</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4490862758579226</v>
+        <v>-0.4545911257889372</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5868143595173905</v>
+        <v>-0.5924486239446836</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2349707923367035</v>
+        <v>-0.2407729884225489</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1899535564175707</v>
+        <v>-0.1957607087315765</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.05378333883321318</v>
+        <v>0.0478300321914773</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.3008822817765946</v>
+        <v>0.2948719202408796</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1467293906809957</v>
+        <v>-0.152597052073375</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6833572339069462</v>
+        <v>-0.6701762246117084</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.7790793423114692</v>
+        <v>-0.765880603356706</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.193482247226704</v>
+        <v>-1.199132733019894</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.274927660938111</v>
+        <v>-1.280575429622878</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.534252020229744</v>
+        <v>-1.539809379570279</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.205302956933153</v>
+        <v>-1.211023577523775</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.527595895685472</v>
+        <v>-1.522339494012883</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2787600143580491</v>
+        <v>-0.2831138327321483</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.6768101220487424</v>
+        <v>-0.6811742218846391</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4397059390267302</v>
+        <v>-0.4441826933467539</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3890449828914768</v>
+        <v>-0.3935296329628528</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1259428608010893</v>
+        <v>0.121243311912913</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.14975590978068</v>
+        <v>0.1450712687832834</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4355413440337728</v>
+        <v>-0.4400462682170172</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.8379369229254081</v>
+        <v>-0.8247559136301703</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8989368091077097</v>
+        <v>-0.8857380701529465</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.277796735879754</v>
+        <v>-1.282142127253785</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.302713479245668</v>
+        <v>-1.307070731490356</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.542333016836395</v>
+        <v>-1.54661223091108</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.4258695979007</v>
+        <v>-1.430224836942017</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.580029380435633</v>
+        <v>-1.575809169567776</v>
       </c>
     </row>
     <row r="28">
@@ -5052,153 +5052,153 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3276</v>
+        <v>3277</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7598616778742127</v>
+        <v>-0.7630686605130634</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.8041296697121112</v>
+        <v>-0.8074305907514656</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7262957341104439</v>
+        <v>-0.7296480748272103</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5492317689593733</v>
+        <v>-0.5526313227685122</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1577442155363471</v>
+        <v>-0.1613001705241786</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2091447071515731</v>
+        <v>-0.2126674205031804</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5515257546866863</v>
+        <v>-0.5549516766722675</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6974217975562382</v>
+        <v>-0.7008358833563761</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6974646584413691</v>
+        <v>-0.6842659194866059</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9212099473935993</v>
+        <v>-0.9246144628448221</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9871549645979059</v>
+        <v>-0.9905547584887628</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.240968498121454</v>
+        <v>-1.244290546284731</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.095155653881541</v>
+        <v>-1.098551748498771</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.255822258694437</v>
+        <v>-1.252568260019309</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.8729</t>
+          <t>X &lt; 0.8728</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3452</v>
+        <v>3453</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6319664587381126</v>
+        <v>-0.6344070865066485</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5830719793636021</v>
+        <v>-0.5856086171046826</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5870882632187033</v>
+        <v>-0.5896448709398214</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4990324753897823</v>
+        <v>-0.5016093812245757</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3573408343418265</v>
+        <v>-0.3599870224243915</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3909536053290807</v>
+        <v>-0.393576601314173</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4021921930323558</v>
+        <v>-0.4048176000927839</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6801641550559694</v>
+        <v>-0.6827340447909549</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6675503994258563</v>
+        <v>-0.6701284023413479</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6627693421542133</v>
+        <v>-0.6653928172290691</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6778234249002608</v>
+        <v>-0.6804542616504534</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.9168622192423754</v>
+        <v>-0.9194235794135892</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8577287163965153</v>
+        <v>-0.8603297473562392</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.11327779401789</v>
+        <v>-1.11076253386414</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.9133</t>
+          <t>X &lt; 0.9132</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3619</v>
+        <v>3620</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4284603466416925</v>
+        <v>-0.4302691821996376</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3181763506900737</v>
+        <v>-0.3200756918801275</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5604867003768774</v>
+        <v>-0.5623348137787261</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6358165399547246</v>
+        <v>-0.6376401003020504</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4427786009565509</v>
+        <v>-0.4446761377558417</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5438849758625395</v>
+        <v>-0.5457447041019847</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5585506507165476</v>
+        <v>-0.5604104482084793</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7349376936770611</v>
+        <v>-0.7367670501310997</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6429498353210406</v>
+        <v>-0.6448078064218379</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7327712461421072</v>
+        <v>-0.7346367801133482</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5633277516508386</v>
+        <v>-0.5652486181792185</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6516413425670891</v>
+        <v>-0.653537584436755</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6145499927948137</v>
+        <v>-0.6164730195602743</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9019798835754784</v>
+        <v>-0.9001201746697163</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3759</v>
+        <v>3760</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3208312173883172</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3261734287987395</v>
+        <v>-0.3275209995260724</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4415252021050406</v>
+        <v>-0.4428533545478572</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4030581253644314</v>
+        <v>-0.4043937228550476</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3167536054626723</v>
+        <v>-0.3181270927079964</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3499218893778107</v>
+        <v>-0.3512793871638991</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2609273313194578</v>
+        <v>-0.2623114123443031</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4480484689667108</v>
+        <v>-0.4493959980229292</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3616746900502861</v>
+        <v>-0.3630474913602484</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3999843424986906</v>
+        <v>-0.4013703053424891</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4038674741981723</v>
+        <v>-0.4052585819819541</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3546280193728393</v>
+        <v>-0.3560320281326312</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3876780050200423</v>
+        <v>-0.3890851588132662</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6018362695129227</v>
+        <v>-0.6005139680163722</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3878</v>
+        <v>3879</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1675580837668988</v>
+        <v>-0.1684802648611807</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1718499794467263</v>
+        <v>-0.1728011726858156</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3214285955435088</v>
+        <v>-0.3223490867593881</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2029608404966581</v>
+        <v>-0.2039098715789578</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2900914286929179</v>
+        <v>-0.2910284528399814</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.235928452044277</v>
+        <v>-0.2368744104791247</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1779659844175896</v>
+        <v>-0.1789289052373846</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.29640649583623</v>
+        <v>-0.2973480392835128</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2917699881465978</v>
+        <v>-0.292714337193523</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.226147683787957</v>
+        <v>-0.2271251214938772</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3134448109171899</v>
+        <v>-0.3144040441222629</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3419572830858826</v>
+        <v>-0.3429090298864281</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2579834687006297</v>
+        <v>-0.2589651260297003</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5094466928242909</v>
+        <v>-0.5085087352573225</v>
       </c>
     </row>
     <row r="33">
@@ -5315,46 +5315,46 @@
         <v>3971</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.00849856117383041</v>
+        <v>0.004023728501792334</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1255994300358978</v>
+        <v>-0.1126896204598467</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1804431711620751</v>
+        <v>-0.1925490482828991</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.08678400050670376</v>
+        <v>-0.09892417486282312</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.310058772486741</v>
+        <v>-0.2969479681118017</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1999508408153901</v>
+        <v>-0.2120398872201861</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1704536239640575</v>
+        <v>-0.1825256300959595</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1461799227008385</v>
+        <v>-0.1581434947483302</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1681917948042084</v>
+        <v>-0.1801439612820346</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2497496007146509</v>
+        <v>-0.2615017057662357</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2139835744104275</v>
+        <v>-0.2256898438607564</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2158288543361522</v>
+        <v>-0.2275464624194683</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1184530044843797</v>
+        <v>-0.1300731917682256</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3329608787693488</v>
+        <v>-0.3433905144675009</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01623841880499555</v>
+        <v>-0.01664791816372713</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1848935899789623</v>
+        <v>-0.1852744183972916</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2458732414970797</v>
+        <v>-0.2462423446451325</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.05290328417368073</v>
+        <v>-0.05331914158359297</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2818459095041845</v>
+        <v>-0.2822097481516295</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1930352149245707</v>
+        <v>-0.193418810505257</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1655947599999621</v>
+        <v>-0.1659859947769249</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1995609376106557</v>
+        <v>-0.1999476802193811</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1481965454617651</v>
+        <v>-0.1485966527394211</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2436094460921367</v>
+        <v>-0.2439929179763993</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1874707418637058</v>
+        <v>-0.1878699035769671</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2133715856170895</v>
+        <v>-0.2137642802310893</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1500586693547845</v>
+        <v>-0.1504705456626851</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2572823877510118</v>
+        <v>-0.2568732768557567</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.001987416448372414</v>
+        <v>-0.002283551901868464</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.01265913571515398</v>
+        <v>-0.01296191841986882</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1254915879624221</v>
+        <v>-0.1257691838968285</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03083503588490544</v>
+        <v>-0.03113516828392449</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2136721941181321</v>
+        <v>-0.2139308291291897</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1474128495724116</v>
+        <v>-0.1476861376142224</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1209765096198936</v>
+        <v>-0.1212568838330412</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1588537268520582</v>
+        <v>-0.1591276270905055</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1329706785816569</v>
+        <v>-0.1332513996484721</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1862560709270511</v>
+        <v>-0.1865287193145591</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1814385350828047</v>
+        <v>-0.1817136682418692</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1333162242323525</v>
+        <v>-0.1336030890172637</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.09886463652107835</v>
+        <v>-0.09916247435100445</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1293282076720885</v>
+        <v>-0.1290486871256888</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/bb_pct_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/bb_pct_14.xlsx
@@ -568,209 +568,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03578</t>
+          <t>X ≈ -0.03567</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17.73212317215461</v>
+        <v>18.36431823282513</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03804611688357795</v>
+        <v>0.9539493500173677</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.959222872754083</v>
+        <v>3.162256618315084</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.997721394286664</v>
+        <v>-1.954397692191982</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.857536210296118</v>
+        <v>0.164881528809552</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.542294196182425</v>
+        <v>0.4445149758723232</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.769145432927857</v>
+        <v>5.634934393627766</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.605051028722315</v>
+        <v>2.523163191128894</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.154705934682944</v>
+        <v>-0.1498478118404734</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.704183081167976</v>
+        <v>-1.013874116998217</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4915665902129618</v>
+        <v>2.877746911628648</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.227400296835164</v>
+        <v>4.417368291805708</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.595991892662823</v>
+        <v>-1.23853587099358</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.370927999068698</v>
+        <v>-0.9898253988204431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.004605</t>
+          <t>X ≈ 0.0047</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1734360214217219</v>
+        <v>-0.9456873306042937</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.448342751836826</v>
+        <v>-10.31755349272776</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.707395323462919</v>
+        <v>-4.476895254656469</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.560233615391461</v>
+        <v>1.889241299196385</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.4883811616022058</v>
+        <v>-0.1587370938943806</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.820496974145648</v>
+        <v>-4.566638682632899</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.370271000854785</v>
+        <v>-3.067831220281548</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.445814070588405</v>
+        <v>-6.655937046065695</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.89883645274891</v>
+        <v>-2.010472626744239</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.8620689608625156</v>
+        <v>0.2889915956916553</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.6577552056295559</v>
+        <v>0.08498695396980338</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.767631119403163</v>
+        <v>3.266576106183827</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2723275089663417</v>
+        <v>-0.2519324266384118</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.194212822354224</v>
+        <v>-7.815483293556092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.04499</t>
+          <t>X ≈ 0.04507</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>65</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.706812936363988</v>
+        <v>-1.736677104604603</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-6.379882715045113</v>
+        <v>-6.384418363452369</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.6387539556102553</v>
+        <v>-0.6392060597298084</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.112681023579754</v>
+        <v>-5.115834055107186</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.581527698190477</v>
+        <v>-2.534304095511288</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.820237300725736</v>
+        <v>-3.798353116568457</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.905843795606643</v>
+        <v>-3.859962447979306</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.301012632436169</v>
+        <v>-1.252569636782631</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.435209770535167</v>
+        <v>-4.364390724186372</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.7486302237714</v>
+        <v>-3.651312486086944</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.028675010893735</v>
+        <v>-6.93066908326945</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.533836751056327</v>
+        <v>-8.410218807962593</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-7.418016908240837</v>
+        <v>-7.269372622964006</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.194212822352824</v>
+        <v>-7.022214062786858</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.08539</t>
+          <t>X ≈ 0.08543</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>96</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5.831833237075244</v>
+        <v>5.264146849715203</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.228648401998363</v>
+        <v>3.666136104392969</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.874295637157232</v>
+        <v>5.350058620867735</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.927719134024997</v>
+        <v>2.362764753609447</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.390969339624249</v>
+        <v>1.871276040305602</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.688904616977027</v>
+        <v>3.1852013923071</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.565200857089103</v>
+        <v>2.084373370672289</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.06097632812633</v>
+        <v>-2.548177992118639</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.082273029398998</v>
+        <v>-1.546120377919799</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.053742855667366</v>
+        <v>-5.957720881370143</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.218967284528269</v>
+        <v>-5.120565596183866</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.186044568236646</v>
+        <v>-5.062425433190711</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.648906099458152</v>
+        <v>-6.500263371918557</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-6.424982053123223</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="10">
@@ -783,150 +783,150 @@
         <v>114</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>6.267733545359732</v>
+        <v>6.209778341475129</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.288201162389775</v>
+        <v>8.098159977061215</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.39440341986923</v>
+        <v>10.33035729771085</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.028080419286091</v>
+        <v>7.835175241360922</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.242117838297766</v>
+        <v>2.085131143012859</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.961436512542292</v>
+        <v>-1.542913394627256</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.171000712963533</v>
+        <v>-0.7280634436813145</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.637557578932153</v>
+        <v>-1.198326177171261</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.80519757002466</v>
+        <v>1.879606817299987</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.08035399188727155</v>
+        <v>0.1795063223730367</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.87713062844638</v>
+        <v>-1.777907912363908</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.08994942953231089</v>
+        <v>0.03367298892786863</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3668468516523262</v>
+        <v>0.5154922339525783</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.346947771439041</v>
+        <v>2.518946531005319</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.1661</t>
+          <t>X ≈ 0.1662</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>136</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.189142234188282</v>
+        <v>1.515553655309013</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.516756921797061</v>
+        <v>2.12364783191402</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.25433485176103</v>
+        <v>7.603794897300382</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.920477200053355</v>
+        <v>6.26652568024646</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.118650685495197</v>
+        <v>6.510501578166618</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.417932353030565</v>
+        <v>6.782937124003439</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.39967326587778</v>
+        <v>3.784306312225127</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.402550813951237</v>
+        <v>4.456364504411873</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.139984283309353</v>
+        <v>2.214756208182017</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.9118087844411065</v>
+        <v>-0.813227502616968</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.822159785380862</v>
+        <v>1.92237656625354</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.326627308523165</v>
+        <v>3.450250370314755</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.907416127625517</v>
+        <v>3.056060608768554</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.9279591233476623</v>
+        <v>1.099957882914659</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.2065</t>
+          <t>X ≈ 0.2066</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>149</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.203358415330122</v>
+        <v>1.177479119928591</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2686816194211232</v>
+        <v>0.2683270610837027</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.218771529953386</v>
+        <v>3.225443884570062</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.343025893264752</v>
+        <v>1.345525849184035</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.484115057471364</v>
+        <v>3.539429719334471</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.443637423469255</v>
+        <v>2.471154763465663</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.369331992990034</v>
+        <v>4.423577807413295</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5545985791623949</v>
+        <v>0.6042880724694157</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1762328842192318</v>
+        <v>-0.1033694259308078</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.695420309533432</v>
+        <v>-1.597362444120336</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5593826587017716</v>
+        <v>-0.4598403589423938</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5253813785562329</v>
+        <v>-0.4017712063064138</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.958474536162683</v>
+        <v>-2.80983911057421</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7202840665454175</v>
+        <v>-0.5482853069790679</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>174</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.237357024070349</v>
+        <v>0.914946063643832</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.360040975457771</v>
+        <v>-2.985100327079905</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.610661568018436</v>
+        <v>-1.654844738867858</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.384825673683352</v>
+        <v>1.344197145377102</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2751485799478033</v>
+        <v>0.276559501161401</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.0001933037060624088</v>
+        <v>-0.0264939359043197</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.80506768688614</v>
+        <v>-2.073166349533949</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.992344697707907</v>
+        <v>-4.266251410557629</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.2019952132976</v>
+        <v>-5.453088586802828</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-7.200238638250646</v>
+        <v>-7.431851050809769</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.110363266373376</v>
+        <v>-4.764577611191577</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.226518141735767</v>
+        <v>-5.854532863531247</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.499445293189154</v>
+        <v>-5.350818201494221</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.275556765766432</v>
+        <v>-5.678270649877923</v>
       </c>
     </row>
     <row r="14">
@@ -991,98 +991,98 @@
         <v>163</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.9466940240324675</v>
+        <v>-0.9760742437337839</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.340110505545681</v>
+        <v>2.345318213292281</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.722798959663891</v>
+        <v>-1.725369565216887</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3694982460374021</v>
+        <v>-0.3695408475231758</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3170819054260292</v>
+        <v>0.3680156127808871</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.6086217297526773</v>
+        <v>-0.5857467036242028</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.143293902758771</v>
+        <v>1.193552841938782</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.06588378189866972</v>
+        <v>0.1146792177110214</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.90522284460922</v>
+        <v>4.984165713375155</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.832905631214423</v>
+        <v>2.934126481510781</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.790248060958028</v>
+        <v>0.8901196538209888</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8245649728712152</v>
+        <v>0.9482467224597642</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.631227015248101</v>
+        <v>1.779854809115577</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.47072346834964</v>
+        <v>2.642722227916302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.3277</t>
+          <t>X ≈ 0.3276</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.201960873735622</v>
+        <v>-1.694170933294558</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.093673152354285</v>
+        <v>1.103700903558831</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.1545509049139042</v>
+        <v>0.1620246224866975</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.008104772825085</v>
+        <v>3.038433508627158</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2513916768985283</v>
+        <v>-0.4508601862122319</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.13668310861911</v>
+        <v>0.9205268332051304</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5827165638213927</v>
+        <v>-0.7878817687109105</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.04811468144328</v>
+        <v>-1.25341505267874</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.746121422802688</v>
+        <v>-2.938184541381958</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.412440460052153</v>
+        <v>-1.564510644584196</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.709436315844876</v>
+        <v>-2.317846471088281</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.406690093569956</v>
+        <v>-5.006033747012637</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-6.375028234784523</v>
+        <v>-5.950287227072629</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.41951757224831</v>
+        <v>-2.956279996852672</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.973482889404607</v>
+        <v>-5.250736163224737</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.161175986795023</v>
+        <v>-1.893700498537157</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.663506511849938</v>
+        <v>-3.38621705523137</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.980342985255831</v>
+        <v>-2.708093776913934</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.305393620945239</v>
+        <v>-1.000119219707834</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.31596255535591</v>
+        <v>2.56822530473309</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.540242559419525</v>
+        <v>-0.2386021600969599</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6526022564807761</v>
+        <v>0.943652549129979</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.072874609729517</v>
+        <v>-0.7410429974873267</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.374162136548854</v>
+        <v>-1.015157126375776</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.639470374181613</v>
+        <v>0.4285384942294925</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.658668199580525</v>
+        <v>-2.808778353586547</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.027745661773871</v>
+        <v>2.838007792324724</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.352795724655017</v>
+        <v>0.8898738493009262</v>
       </c>
     </row>
     <row r="17">
@@ -1144,777 +1144,777 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.273967518670048</v>
+        <v>-0.9755120606608685</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.914022470735965</v>
+        <v>-3.169526202576122</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-8.884399286039034</v>
+        <v>-9.081651192005403</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-4.702290543209195</v>
+        <v>-5.275596894504197</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.627857492073396</v>
+        <v>-5.151388380275883</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.007485041198329156</v>
+        <v>-0.5858108973821459</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.84234926311634</v>
+        <v>-3.712600298901826</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.314698167504154</v>
+        <v>-4.178090847846349</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.618942146820928</v>
+        <v>-5.441508226614722</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1075321862181084</v>
+        <v>-0.745501203705615</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.582014110326853</v>
+        <v>-3.402616743364618</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.929649896321891</v>
+        <v>-2.731092162489325</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.992332610181727</v>
+        <v>-3.126178795003561</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.387714972377552</v>
+        <v>-3.492247097237076</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.4488</t>
+          <t>X ≈ 0.4487</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-10.31276748838488</v>
+        <v>-10.59357958710959</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-11.91730057193213</v>
+        <v>-11.62055044290176</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-10.07547413890649</v>
+        <v>-9.786151121685954</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.26605277718955</v>
+        <v>-7.985245166590978</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.883619298732199</v>
+        <v>-4.565304807097895</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.225014207143019</v>
+        <v>-0.9420974602074637</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.793380673157024</v>
+        <v>-5.469895719949463</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.457058902188457</v>
+        <v>-3.143210422194663</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.836117969130242</v>
+        <v>-1.504792816789397</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.808925280360839</v>
+        <v>-3.445032039174748</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.330863077090065</v>
+        <v>-1.97376597212255</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.545173591608908</v>
+        <v>-4.149202920108252</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.403526692113324</v>
+        <v>-3.985853975035205</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-5.863184300313762</v>
+        <v>-5.414994466740453</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.4892</t>
+          <t>X ≈ 0.4891</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.85091136467225</v>
+        <v>-2.839939653839572</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.656053243912666</v>
+        <v>3.621192004183591</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.617872099595239</v>
+        <v>4.569882739200345</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.039734745236458</v>
+        <v>2.017877234343885</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.499029626203928</v>
+        <v>1.528740214422861</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.492553786929761</v>
+        <v>1.130422794396722</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7237545667240823</v>
+        <v>0.399373866188391</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.290351221424324</v>
+        <v>1.946420125055425</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8695114683327247</v>
+        <v>0.5678396170599527</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6683504154648503</v>
+        <v>-0.9262883685455918</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.596690462960112</v>
+        <v>-3.81370067431493</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.849614469083342</v>
+        <v>-4.426188391671552</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8684047781792259</v>
+        <v>-1.467064955349208</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.363757563326836</v>
+        <v>-3.90399000496533</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.5296</t>
+          <t>X ≈ 0.5295</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>148</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.831149564950096</v>
+        <v>-2.548982974363049</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-7.820208272122152</v>
+        <v>-7.53281494421384</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.452999161567682</v>
+        <v>-2.526029756637428</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.694141993633046</v>
+        <v>-6.076194498069526</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.257785673963554</v>
+        <v>-8.594280511608453</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-10.65905343426427</v>
+        <v>-11.02027636344595</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-8.718478313327388</v>
+        <v>-9.061446448810138</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.140708353082857</v>
+        <v>-5.478051409965765</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.879313387198415</v>
+        <v>-6.192509540338058</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.40727093605387</v>
+        <v>-7.701063024627814</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.589269326715375</v>
+        <v>-5.880891213476609</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.230566850036034</v>
+        <v>-6.501718201980388</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.002069054700485</v>
+        <v>-8.247925838969081</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.803360431500984</v>
+        <v>-9.631361671934627</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.57</t>
+          <t>X ≈ 0.5698</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.498069495644501</v>
+        <v>-2.506714799361738</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4781137673206075</v>
+        <v>-0.4691904012618764</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1429506376721719</v>
+        <v>-0.1392008114011887</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7399054374474971</v>
+        <v>-0.7339544513455962</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.307611895535381</v>
+        <v>0.9507094511809058</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.60410395484891</v>
+        <v>1.223494969999678</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.249981544144909</v>
+        <v>1.887476561933632</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.699422433772142</v>
+        <v>4.320194526187805</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.38040660821494</v>
+        <v>-3.687792575702773</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5843354350702157</v>
+        <v>-0.8884327507204901</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.980273469544649</v>
+        <v>-3.266486241735173</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7561142952911837</v>
+        <v>-1.034406460892022</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4463381413054961</v>
+        <v>-0.7049267062962628</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.680456505677668</v>
+        <v>-1.905157206599405</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.6103</t>
+          <t>X ≈ 0.6102</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.54925713047691</v>
+        <v>2.59021764895715</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.736112473610874</v>
+        <v>-1.710595427005238</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.462025765506162</v>
+        <v>-1.425802408561466</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.001907575192376</v>
+        <v>-2.656462585034014</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.539515931698091</v>
+        <v>-3.145711725986089</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.582469341377269</v>
+        <v>-4.233470424854005</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.353121420709094</v>
+        <v>-0.2124938610184728</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.463968215924538</v>
+        <v>-4.079687165619347</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8448148635176125</v>
+        <v>-1.395571339381995</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.707828108441788</v>
+        <v>-4.260216246727744</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5602470158138644</v>
+        <v>-1.062996150045848</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5258688634586974</v>
+        <v>-1.004829412680799</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.288301595966892</v>
+        <v>-2.760531556931845</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.391425006142889</v>
+        <v>-1.831214586073251</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.6507</t>
+          <t>X ≈ 0.6506</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.51797329543222</v>
+        <v>-2.505929869350567</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.328246968904232</v>
+        <v>-2.305135727703068</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.109146799870992</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7590759986024338</v>
+        <v>-0.1904761904761969</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.744047394533375</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.826418779781079</v>
+        <v>-2.192654098323537</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.093206827371326</v>
+        <v>-0.4675959018346489</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.267827182848038</v>
+        <v>-3.909619138408466</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.89918320936598</v>
+        <v>-1.565639366592819</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.542089972975511</v>
+        <v>-1.198991756931534</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4423720707793279</v>
+        <v>0.3825820812465182</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.352518069548282</v>
+        <v>-1.344965467103009</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.05659936982151947</v>
+        <v>0.04559089204758493</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.892091117608885</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.6911</t>
+          <t>X ≈ 0.6909</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>170</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.888408504223335</v>
+        <v>-1.648009046569285</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.378071217868751</v>
+        <v>2.634988734144883</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.982551262882744</v>
+        <v>1.983561336936575</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3500588832150981</v>
+        <v>0.3487394957983199</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1881474954105187</v>
+        <v>-0.1405096451535996</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.633913010505871</v>
+        <v>3.661687638371212</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.324138091471141</v>
+        <v>-2.281321392030719</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.789875943736497</v>
+        <v>-2.747154152414062</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.502341293769895</v>
+        <v>-0.4311855850803497</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.175050273516057</v>
+        <v>2.274397598810694</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.205643232902986</v>
+        <v>0.3055512689215902</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.181197855846541</v>
+        <v>3.304894476874722</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.525752884885875</v>
+        <v>4.674442432663838</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.163253240994955</v>
+        <v>4.335252000561553</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.7315</t>
+          <t>X ≈ 0.7313</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.467642811017257</v>
+        <v>5.20139503484657</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.426922460147587</v>
+        <v>4.192425375671384</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.896597477136254</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.02661172322918</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.055729898644778</v>
+        <v>2.867893716190935</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.189088083359394</v>
+        <v>5.997822092152724</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.07781355488746</v>
+        <v>9.937166002927256</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>7.343222972009436</v>
+        <v>7.1856189568297</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>8.421785693365685</v>
+        <v>8.291503490550035</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.439756155868992</v>
+        <v>6.324817766877786</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.666873179426979</v>
+        <v>5.549248747913182</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.701251331782245</v>
+        <v>5.607415485278075</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.281100478468957</v>
+        <v>5.212257558714185</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.802290674149972</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.7719</t>
+          <t>X ≈ 0.7717</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.106559175093771</v>
+        <v>2.569343765515299</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.911495917876721</v>
+        <v>-1.666104444023475</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.271668595650659</v>
+        <v>-3.030716218745894</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.14172879540169</v>
+        <v>-2.900832177531264</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.141994608157979</v>
+        <v>1.464287613555754</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.937467148562703</v>
+        <v>-1.660985120052551</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-4.43104391111109</v>
+        <v>-4.148825675297488</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.96645393884198</v>
+        <v>-2.672910862865237</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.548947189621565</v>
+        <v>-2.224446578798208</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.437055438333957</v>
+        <v>-2.077401373205369</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.675573021714875</v>
+        <v>-1.310668034333695</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.641194869359495</v>
+        <v>-1.252501296968802</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.476804659871028</v>
+        <v>-3.589406796348101</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.31870185988604</v>
+        <v>-1.398614361517204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.8123</t>
+          <t>X ≈ 0.8121</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8.415631763380297</v>
+        <v>-8.347675276663665</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.831045124973841</v>
+        <v>-2.82425337704786</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.283500533256628</v>
+        <v>-5.24844821815455</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.092994429404818</v>
+        <v>-3.088107324147884</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-4.6573435620477</v>
+        <v>-4.592584891495825</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.903510793280049</v>
+        <v>-5.842642012270744</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.391447759697797</v>
+        <v>-2.349998609110393</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.25462569779765</v>
+        <v>1.245082336089908</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.52227486594267</v>
+        <v>2.223338153349111</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.764498423910347</v>
+        <v>4.445194851721944</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.044333348124205</v>
+        <v>3.733440190987885</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.563247582953814</v>
+        <v>3.283992715154803</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.174024564691891</v>
+        <v>3.396449001788952</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.884296297392709</v>
+        <v>3.137879650606344</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.8527</t>
+          <t>X ≈ 0.8524</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.74980409203971</v>
+        <v>1.512876680860174</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.534940777321161</v>
+        <v>3.377975457773253</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.004444162739745</v>
+        <v>1.834812182102262</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.433954291006323</v>
+        <v>0.8152709359605836</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.076500737063839</v>
+        <v>-3.696966710738494</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.779126707428752</v>
+        <v>-3.424181191919565</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.377863648320393</v>
+        <v>1.687576511958454</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3670395204919146</v>
+        <v>0.07231846421878885</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4286600835518612</v>
+        <v>0.03534585508196386</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.167028883141654</v>
+        <v>4.383931067370462</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.098691361245265</v>
+        <v>4.754503263512504</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.133069513600489</v>
+        <v>5.387382644555579</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.576555023923511</v>
+        <v>3.842799430635438</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.529563401422706</v>
+        <v>1.792993717938096</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.893</t>
+          <t>X ≈ 0.8928</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.806509119166243</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.189335002150322</v>
+        <v>6.025758709004776</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.004144455718602558</v>
+        <v>0.8701159587853198</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.458444771950482</v>
+        <v>-3.166666666666707</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.200327139417467</v>
+        <v>-1.870201521904271</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.69936029541109</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.784070654677258</v>
+        <v>-2.253310187548927</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.855929717625649</v>
+        <v>-1.528666757456087</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.1205046885197447</v>
+        <v>0.2200749191214442</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.168028275268732</v>
+        <v>-1.794229852169771</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.818887332938111</v>
+        <v>2.76353446219894</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.84727746134137</v>
+        <v>5.202653580516177</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.427126608027962</v>
+        <v>4.807495653952351</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.455257467835324</v>
+        <v>3.866064325491521</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.9334</t>
+          <t>X ≈ 0.9332</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.519083969465655</v>
+        <v>2.099817253127178</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5206735521696544</v>
+        <v>-0.901799548340712</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.655983634503961</v>
+        <v>2.250561754124767</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.217325227963563</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.962204939282344</v>
+        <v>2.600416512543454</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.688150397488819</v>
+        <v>4.291641747674497</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.460582895365533</v>
+        <v>7.06786509107318</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.993514251578752</v>
+        <v>6.602032330689809</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.932532095055997</v>
+        <v>6.565059721553013</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.225470441583283</v>
+        <v>7.86889071520612</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.735054997608778</v>
+        <v>3.409431118733856</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.340861721392692</v>
+        <v>7.013697146878869</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.492139439507859</v>
+        <v>5.200099504002985</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.146446518305858</v>
+        <v>6.867584082330438</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.9738</t>
+          <t>X ≈ 0.9735</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>119</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.661941112322765</v>
+        <v>4.632745317970176</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>4.730240501721873</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.496319768957711</v>
+        <v>3.49616637895339</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.147553315907409</v>
+        <v>6.147058823529406</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.5672469560890292</v>
+        <v>0.6157928758548223</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.385629389085466</v>
+        <v>3.409586798035079</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.460582895365484</v>
+        <v>1.668258439902026</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.514522654940137</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.932532095056011</v>
+        <v>1.165453070381908</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.284293970995066</v>
+        <v>4.543305161835832</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.558584409373552</v>
+        <v>1.818156310938406</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.07195415836746122</v>
+        <v>-0.64468535505803</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.853483977322981</v>
+        <v>3.161837390647051</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>2.398547358641935</v>
+        <v>1.730209983754804</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.301692665117855</v>
+        <v>6.629673121349576</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.4296370068366</v>
+        <v>1.820689584580812</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.295735187298952</v>
+        <v>4.652758047879018</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.339003809148167</v>
+        <v>3.707373271889381</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5471118309040364</v>
+        <v>-1.082951137879732</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.8372187204701902</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3344481605351177</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.720222326112939</v>
+        <v>6.190227251760504</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.572283647850988</v>
+        <v>5.077985825419411</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.712417757174521</v>
+        <v>-1.122186841417083</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.517663693260936</v>
+        <v>4.050016797068338</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.638998367355455</v>
+        <v>5.183452351637527</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.305804035781144</v>
+        <v>5.863563242278005</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>6.618496207746816</v>
+        <v>7.18787692149774</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.129564679183005</v>
+        <v>-1.825180318037667</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.778220416892168</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.13552215700188</v>
+        <v>-2.432232377809612</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.400108391991921</v>
+        <v>3.177103718199625</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5104674875448509</v>
+        <v>1.317991563549057</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.8078415171799165</v>
+        <v>1.590777082367964</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.7231311579137483</v>
+        <v>1.530120993142503</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.446640188575685</v>
+        <v>-1.675437794638057</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.546431708955581</v>
+        <v>1.027315623622407</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.6965129126257494</v>
+        <v>0.2034870428074029</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.843163105716904</v>
+        <v>1.369209608969939</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.5261899067208518</v>
+        <v>0.05751333263620495</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.245312297943883</v>
+        <v>-1.707507607626255</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.38582875768801</v>
+        <v>4.020989309183598</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.573138023519704</v>
+        <v>2.753046069849866</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>18.88087084937482</v>
+        <v>19.590921616273</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.08069405921437</v>
+        <v>11.30244678585301</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.400108391991921</v>
+        <v>0.9060150375939955</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.26722424430163</v>
+        <v>5.679923791378926</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.861895571234029</v>
+        <v>3.321130362829443</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.777185211967861</v>
+        <v>3.260474273603982</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.310116568181122</v>
+        <v>2.794641513220562</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.546431708955652</v>
+        <v>2.757668904083765</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.101918318031153</v>
+        <v>7.196998218005668</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4918117543655569</v>
+        <v>1.729699875732742</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.634298014829049</v>
+        <v>9.682603455202916</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.511444458812875</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>13.84528821714752</v>
+        <v>14.79964828539128</v>
       </c>
     </row>
   </sheetData>
@@ -2210,209 +2210,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.05597</t>
+          <t>X &gt; -0.05585</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07554362516194146</v>
+        <v>-0.07465152288990851</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03738790767243216</v>
+        <v>-0.03725967739971736</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04525451510145473</v>
+        <v>0.04513684433251086</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.06661654237101544</v>
+        <v>0.06644963615472932</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.06726742164935473</v>
+        <v>-0.06823500150774464</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.07236276214128878</v>
+        <v>0.07160200645933656</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1233016879449025</v>
+        <v>0.1218349924742981</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01210524962181836</v>
+        <v>0.01090735469669823</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1114268484552738</v>
+        <v>0.109393750607147</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0582094108861213</v>
+        <v>0.0557009915370088</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1610035900200586</v>
+        <v>0.1582052211274743</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2091980863010434</v>
+        <v>0.2057060835686784</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1212636828863296</v>
+        <v>0.1174149318735829</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.09143146966019344</v>
+        <v>0.08710954788050174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01559</t>
+          <t>X &gt; -0.01548</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4045</v>
+        <v>4055</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2384320482770832</v>
+        <v>-0.2474458140655358</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.03738188697013101</v>
+        <v>-0.04654844263816216</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0003059788262618213</v>
+        <v>0.01592585754796971</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.09464633313896087</v>
+        <v>0.08538729299250747</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.08487378367210141</v>
+        <v>-0.07041957071910332</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.07798508784164682</v>
+        <v>0.06810738430454677</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.08080571302169659</v>
+        <v>0.07017092903562627</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.002465577034982402</v>
+        <v>-0.01263536337591376</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1230082855321868</v>
+        <v>0.1118231413279887</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1017714682918083</v>
+        <v>0.06572413682045664</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.1579798987945651</v>
+        <v>0.1327199969008319</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1815903034111201</v>
+        <v>0.1662379790278621</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1461186782621837</v>
+        <v>0.1301217458092125</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1139549060861427</v>
+        <v>0.09720166328731494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.0248</t>
+          <t>X &gt; 0.02488</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3980</v>
+        <v>3991</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2394935411779855</v>
+        <v>-0.2362487564212188</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1163147100691546</v>
+        <v>0.1181582281726037</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.06085888954204677</v>
+        <v>0.08797310164245431</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.05437920415744912</v>
+        <v>0.05646054370734532</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09423598755220297</v>
+        <v>-0.06900330374760699</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1416537647334053</v>
+        <v>0.1424305484949713</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1208358603588806</v>
+        <v>0.1204921862534434</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1190966471059767</v>
+        <v>0.09389716172860574</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1723600212076377</v>
+        <v>0.145856448558412</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08935454944328569</v>
+        <v>0.06214380172454526</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1498177392608255</v>
+        <v>0.1334854478523653</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1230243101851158</v>
+        <v>0.1165207051271011</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1440574787657596</v>
+        <v>0.1362483975347573</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.2333094041636841</v>
+        <v>0.2240901216280733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.06518</t>
+          <t>X &gt; 0.06525</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3915</v>
+        <v>3926</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2151319164814041</v>
+        <v>-0.2114072274777854</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2241698397326033</v>
+        <v>0.2258167810140748</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07247442847815933</v>
+        <v>0.1000124917313983</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1401669218593398</v>
+        <v>0.1420945602440185</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.05293995659653206</v>
+        <v>-0.02818706547337513</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2074322881701463</v>
+        <v>0.2076753111615872</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1876900564349313</v>
+        <v>0.1863937530453654</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1426744512362959</v>
+        <v>0.1161896583926989</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.248858625668241</v>
+        <v>0.22052941499458</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1530758802884904</v>
+        <v>0.1236248660922854</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2690008883693906</v>
+        <v>0.2504416486987537</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2667525270384203</v>
+        <v>0.2576918891186395</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2696091607977991</v>
+        <v>0.2588580170794259</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3566271422795424</v>
+        <v>0.3440620452111034</v>
       </c>
     </row>
     <row r="10">
@@ -2422,153 +2422,153 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3819</v>
+        <v>3830</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3671373248976053</v>
+        <v>-0.3486534915536481</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1235073778374769</v>
+        <v>0.139584234005099</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.04823121070308645</v>
+        <v>-0.0315813538030838</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.07009491024167147</v>
+        <v>0.08643285304739123</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1143736545376655</v>
+        <v>-0.07579762896026665</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1450543506038997</v>
+        <v>0.1330428036446207</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1530629192621618</v>
+        <v>0.1388203735957134</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2232061283294726</v>
+        <v>0.1829727639929857</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3074573789770909</v>
+        <v>0.2648109763835578</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3090996034232703</v>
+        <v>0.2760554644620967</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4069545266511909</v>
+        <v>0.3850674177610927</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.4038220533925454</v>
+        <v>0.391042088320134</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4435231343470463</v>
+        <v>0.428277247717503</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.5270996436565127</v>
+        <v>0.509418795216753</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.1459</t>
+          <t>X &gt; 0.146</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3705</v>
+        <v>3716</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.571287197828596</v>
+        <v>-0.5498540375615235</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.09694473861028996</v>
+        <v>-0.1045701348615253</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3695430454899338</v>
+        <v>-0.3494664469873143</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1439969515750832</v>
+        <v>-0.1512842169923658</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.15611185431721</v>
+        <v>-0.1420909228259646</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2098694540853288</v>
+        <v>0.1844580368531794</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1938033387152629</v>
+        <v>0.1654147641149777</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.2804603962452106</v>
+        <v>0.2253484580975993</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2613730654063957</v>
+        <v>0.2152720297031294</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3161379299320828</v>
+        <v>0.2790174133851835</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4772340698849575</v>
+        <v>0.4514234962417802</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.4190150220979234</v>
+        <v>0.4020055106373377</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4458824045837986</v>
+        <v>0.4256016534142759</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4711043166478248</v>
+        <v>0.4477702048292684</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.1863</t>
+          <t>X &gt; 0.1864</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3569</v>
+        <v>3580</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.638369966882756</v>
+        <v>-0.6283164527096758</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1965422241287555</v>
+        <v>-0.1892175213088692</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6600578658951193</v>
+        <v>-0.6516015148150061</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3750892700456561</v>
+        <v>-0.3950892857142918</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3952174036067859</v>
+        <v>-0.3948151072212127</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.02669444455758452</v>
+        <v>-0.06621044243521368</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.07164074132268894</v>
+        <v>0.02793731982922765</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1233843814489006</v>
+        <v>0.06461712225996052</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1897868716168674</v>
+        <v>0.1393139715262848</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3629299593954443</v>
+        <v>0.3205105163394464</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4259844488965996</v>
+        <v>0.3955437148111685</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3082178041226271</v>
+        <v>0.2862062645713763</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3520834170988891</v>
+        <v>0.3256736037136605</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4536954475777293</v>
+        <v>0.4229943600751866</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3420</v>
+        <v>3431</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7186090104353084</v>
+        <v>-0.7067377702040218</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2168107483068056</v>
+        <v>-0.2090875716663447</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.8290478015622043</v>
+        <v>-0.8199721835729079</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4499428254062536</v>
+        <v>-0.4706799750467994</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5642292564432267</v>
+        <v>-0.5656698082287335</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1343200142464696</v>
+        <v>-0.1764020529508699</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1155978541446885</v>
+        <v>-0.1629546745310222</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.104597564063134</v>
+        <v>0.0411805231398148</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2057333463594375</v>
+        <v>0.1498531222756583</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4526066231587151</v>
+        <v>0.403799082678276</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4689141854557093</v>
+        <v>0.4326909683784237</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3445354293329146</v>
+        <v>0.3160834558161412</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4963153279281158</v>
+        <v>0.4618413082980055</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5048425082807526</v>
+        <v>0.4651746778808103</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3246</v>
+        <v>3257</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8234574669984482</v>
+        <v>-0.7933736274620884</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1019241002709848</v>
+        <v>-0.06078354359082283</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.787149836262337</v>
+        <v>-0.7753704566397488</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.548294556411058</v>
+        <v>-0.5676368737123667</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6092236321462678</v>
+        <v>-0.6106645579474517</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1415098009482705</v>
+        <v>-0.1844106536159345</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.02503477623433525</v>
+        <v>-0.06090468022629381</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3242118442689872</v>
+        <v>0.2712981640557999</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4956115870804183</v>
+        <v>0.4491812946366167</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.8628330789459113</v>
+        <v>0.8224061208197924</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7679882078273295</v>
+        <v>0.7103467045912595</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6967730514419586</v>
+        <v>0.6457387335460893</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8177146957883821</v>
+        <v>0.7723733177250409</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8146975525457592</v>
+        <v>0.7933783889738422</v>
       </c>
     </row>
     <row r="15">
@@ -2682,101 +2682,101 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3083</v>
+        <v>3094</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8169418786765164</v>
+        <v>-0.7837484818731113</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2310358877338814</v>
+        <v>-0.1875432676929378</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7376815238671171</v>
+        <v>-0.7253220226713992</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5577476211502486</v>
+        <v>-0.5780730897010073</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.658197943733775</v>
+        <v>-0.662223985170705</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1168133220656458</v>
+        <v>-0.1632672224099423</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.08680499182820256</v>
+        <v>-0.1269927785174687</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.337869798912628</v>
+        <v>0.279549259160575</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2624728796599882</v>
+        <v>0.2102664723178052</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7586741992768324</v>
+        <v>0.7111551774478926</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7668113164681571</v>
+        <v>0.7008757961476704</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.6900166183595786</v>
+        <v>0.6298018226886484</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.7747038271306081</v>
+        <v>0.7192965617144864</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7271425008830832</v>
+        <v>0.6959501259655596</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.3479</t>
+          <t>X &gt; 0.3478</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2900</v>
+        <v>2912</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7295424041607177</v>
+        <v>-0.7268470786592758</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.3146295961256556</v>
+        <v>-0.2682460283961774</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7939844667867462</v>
+        <v>-0.7807811879937745</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7827652032528292</v>
+        <v>-0.8041047520965137</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6838688219513074</v>
+        <v>-0.6754342226056025</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1959132692433414</v>
+        <v>-0.2310043508858826</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.05551126159551956</v>
+        <v>-0.08568721663039014</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4253301988799123</v>
+        <v>0.3753595286505345</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4523255546084854</v>
+        <v>0.4070446606740532</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.895679020882767</v>
+        <v>0.8533842913249075</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.986174529127922</v>
+        <v>0.889545937849924</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.07473983500892</v>
+        <v>0.9820415457949778</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.225876574485937</v>
+        <v>1.136145548513682</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9888110503255163</v>
+        <v>0.924214508641704</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2720</v>
+        <v>2730</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4486934014607513</v>
+        <v>-0.4252544730215817</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1924316732137044</v>
+        <v>-0.159882397053444</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6040896255693369</v>
+        <v>-0.6070854635112752</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6373372617967448</v>
+        <v>-0.6771721504420185</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6427385043708185</v>
+        <v>-0.6537885561321275</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3621403458712322</v>
+        <v>-0.4176196612604741</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.02343345512186801</v>
+        <v>-0.07549288706594126</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.4102901362445621</v>
+        <v>0.3374733272852453</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5532579184249826</v>
+        <v>0.4835838378848081</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.045889097477513</v>
+        <v>0.9779537191716159</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.009118186440539</v>
+        <v>0.920279767424617</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.321803602003811</v>
+        <v>1.234762872420411</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.106635237827177</v>
+        <v>1.022688065592945</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.9647238292301807</v>
+        <v>0.9265038859310835</v>
       </c>
     </row>
     <row r="18">
@@ -2838,777 +2838,777 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2559</v>
+        <v>2567</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3967711142897059</v>
+        <v>-0.3903140808185341</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.02120224046611696</v>
+        <v>0.03122470863420546</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.08313227686451796</v>
+        <v>-0.0689653958273766</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3815899080228462</v>
+        <v>-0.3851802403204303</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3920139412523653</v>
+        <v>-0.3681988516773416</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3853954014860008</v>
+        <v>-0.4069398126091883</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1539192002462784</v>
+        <v>0.1554570576669079</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6446485250306324</v>
+        <v>0.6242037365359039</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8786679264377213</v>
+        <v>0.8598167971810398</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.104926011394177</v>
+        <v>1.087390085524937</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.235054997608792</v>
+        <v>1.194776117739629</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.526369453207579</v>
+        <v>1.486587714917597</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.301607423653451</v>
+        <v>1.286133838198012</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.175643191113274</v>
+        <v>1.207086827207448</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.469</t>
+          <t>X &gt; 0.4689</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2381</v>
+        <v>2388</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3445339485363874</v>
+        <v>0.374503559728403</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8681322841037868</v>
+        <v>0.904619914716676</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6638802604909984</v>
+        <v>0.6594166162868049</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2078407474629529</v>
+        <v>0.1845063684745583</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.05622824044120023</v>
+        <v>-0.05359166322664066</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3226267549480113</v>
+        <v>-0.3668253993260819</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5985304465569783</v>
+        <v>0.5771229484513896</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9512860395392337</v>
+        <v>0.906602034028694</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.081621260923676</v>
+        <v>1.037063497725725</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.472278186922281</v>
+        <v>1.427131944955946</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.501637701219209</v>
+        <v>1.432284088462133</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.980268933248453</v>
+        <v>1.909036007911581</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.728114720002246</v>
+        <v>1.681312154181583</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.701855410127983</v>
+        <v>1.703465617666687</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.5094</t>
+          <t>X &gt; 0.5093</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2234</v>
+        <v>2239</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5547982551799322</v>
+        <v>0.5884169312431951</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.6846835906875341</v>
+        <v>0.7238386546315567</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.403702641713771</v>
+        <v>0.3991846143600029</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.08729982639190581</v>
+        <v>0.0625</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1585661573601058</v>
+        <v>-0.1588919980947807</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4420679096731845</v>
+        <v>-0.4664636221329985</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5902905424994316</v>
+        <v>0.5889517172129715</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8631738722442037</v>
+        <v>0.8374046711153369</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.095578351125511</v>
+        <v>1.068289204835686</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.613134231931632</v>
+        <v>1.583746338306426</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.837114084448551</v>
+        <v>1.781391605056051</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.363882568048268</v>
+        <v>2.330629770992367</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.898968957349012</v>
+        <v>1.890828987285687</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.035179092803837</v>
+        <v>2.076628140119652</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.5498</t>
+          <t>X &gt; 0.5497</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7950284936167691</v>
+        <v>0.8104806261402544</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.288098737233959</v>
+        <v>1.308240726668437</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6063833065678708</v>
+        <v>0.6062299165635494</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4974884118970309</v>
+        <v>0.4969939195190278</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4160668668284444</v>
+        <v>0.4381608474336787</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2828188868941552</v>
+        <v>0.2805302973860364</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.250740106575357</v>
+        <v>1.272002376501078</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.289144423226176</v>
+        <v>1.284409692636146</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.590441235723759</v>
+        <v>1.582205137062232</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.253124627359171</v>
+        <v>2.240920793454336</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.364009935288564</v>
+        <v>2.323724391829288</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.973651750155874</v>
+        <v>2.955779221016272</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.601439535385126</v>
+        <v>2.608445302104293</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.875113824154326</v>
+        <v>2.905314171771501</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.5902</t>
+          <t>X &gt; 0.59</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1949</v>
+        <v>1953</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.026508444632057</v>
+        <v>1.044875387389233</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.41225015494765</v>
+        <v>1.433834938473034</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6590558311245118</v>
+        <v>0.6589024411201905</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.584467866673954</v>
+        <v>0.583973374295951</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.353397975636625</v>
+        <v>0.4019438954023968</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1899425121841603</v>
+        <v>0.2138999211337733</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.180500970122289</v>
+        <v>1.228512649112609</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.049427600524901</v>
+        <v>1.069899550787646</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.939854347380809</v>
+        <v>1.95458592782596</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.45257666868951</v>
+        <v>2.46204254926392</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.739672750302489</v>
+        <v>2.718731594815395</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>3.235826172026712</v>
+        <v>3.237727825267847</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.815675318713303</v>
+        <v>2.842569898704021</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.195336058729481</v>
+        <v>3.24522459174856</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.6305</t>
+          <t>X &gt; 0.6304</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.9004586923037863</v>
+        <v>0.9190917149360303</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.672864616978316</v>
+        <v>1.689776944965459</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.8346342521789296</v>
+        <v>0.8285877195826572</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7985622782506567</v>
+        <v>0.8477297895902538</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5928669601882319</v>
+        <v>0.6907065622595923</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.5022143822845138</v>
+        <v>0.5758951818537099</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.248989610601491</v>
+        <v>1.345803876681408</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.4230364764421</v>
+        <v>1.48905195793705</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.170363076505176</v>
+        <v>2.227273147249868</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.962521286352057</v>
+        <v>3.009203148937658</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.01283277538657</v>
+        <v>3.026546643815735</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.547210927741894</v>
+        <v>3.583052251612514</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.238171185539606</v>
+        <v>3.298636296255786</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.658423129478237</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.6709</t>
+          <t>X &gt; 0.6708</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.243137693519373</v>
+        <v>1.270375979991066</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.073954042457984</v>
+        <v>2.099511578059662</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.129732108252398</v>
+        <v>1.129578718248077</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9547069465904556</v>
+        <v>0.9542124542124526</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4774674545448221</v>
+        <v>0.5260133743105939</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.8358915452299698</v>
+        <v>0.8598489541795828</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.483781918564532</v>
+        <v>1.531793597554852</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.578312704184192</v>
+        <v>2.616289815336295</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.414083784230847</v>
+        <v>3.440812882872969</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.270507320347193</v>
+        <v>3.297722496386939</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.038381805220851</v>
+        <v>4.088489966352562</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.557106257530904</v>
+        <v>3.632281978738675</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.843966602133975</v>
+        <v>3.942376901804103</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.7113</t>
+          <t>X &gt; 0.7111</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.606277429956116</v>
+        <v>1.60833609887068</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.038688067137507</v>
+        <v>2.037501280692851</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.030837663308901</v>
+        <v>1.03068427330458</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.024823024880916</v>
+        <v>1.024328532502913</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.5546533627934025</v>
+        <v>0.6031992825591743</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5114279373876087</v>
+        <v>0.5353853463372218</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.925355180301281</v>
+        <v>1.973366859291602</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.548204792645336</v>
+        <v>2.597452355039053</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.935550889485832</v>
+        <v>2.969199091951296</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.557764341407875</v>
+        <v>3.575888222307974</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.625914479191337</v>
+        <v>3.644227338804583</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.137782399623056</v>
+        <v>4.179233313226703</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.444780250266</v>
+        <v>3.511595822630177</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.806941548514352</v>
+        <v>3.896880466661891</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.7517</t>
+          <t>X &gt; 0.7515</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.079455486493508</v>
+        <v>1.122036552238207</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.712851436773335</v>
+        <v>1.745844887327621</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7762843863836295</v>
+        <v>0.8107302555481084</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7517107683620807</v>
+        <v>0.7859352557728414</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2134212152663864</v>
+        <v>0.2966861148209219</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2631985631480731</v>
+        <v>-0.2039235713098861</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.8130817896600675</v>
+        <v>0.8955131468892503</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.894000761972407</v>
+        <v>1.976470796405358</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.187041334847954</v>
+        <v>2.248856269248456</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.164562357419378</v>
+        <v>3.20383665981786</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.347458098383989</v>
+        <v>3.38639381475663</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.924471909654052</v>
+        <v>3.985937195586331</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.194243536960791</v>
+        <v>3.281421187042625</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.807576086412134</v>
+        <v>3.917163651532853</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.7921</t>
+          <t>X &gt; 0.7919</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.8831392690048148</v>
+        <v>0.8477538604856036</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.405593728936374</v>
+        <v>2.392451660334352</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.549992851093783</v>
+        <v>1.538732071283675</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.495886197447128</v>
+        <v>1.484623472203971</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.03593765817630867</v>
+        <v>0.07541112978010034</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.05681399195886883</v>
+        <v>0.07220768815744805</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.815421605042921</v>
+        <v>1.851478001875876</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.823007339136375</v>
+        <v>2.857586363847631</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.09225797802911</v>
+        <v>3.096602715152422</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.23523168680159</v>
+        <v>4.204696857428516</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.307538838790698</v>
+        <v>4.276545370334006</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.98826971506108</v>
+        <v>4.978686348729255</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.660454965164107</v>
+        <v>4.583528422165429</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.978526718807075</v>
+        <v>4.924569604327985</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.8325</t>
+          <t>X &gt; 0.8322</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.912342396431946</v>
+        <v>2.883146602079314</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.548347314604065</v>
+        <v>3.547160528159409</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.041216379287235</v>
+        <v>3.041062989282914</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.497284219504806</v>
+        <v>2.496789727126803</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.060118261914724</v>
+        <v>1.108664181680496</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.357492291549811</v>
+        <v>1.381449700499424</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.733456089587015</v>
+        <v>2.781467768577336</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.165263850294664</v>
+        <v>3.214511412688381</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3.21664124433368</v>
+        <v>3.289898354113376</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.119733658681135</v>
+        <v>4.151463031725363</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.364976257451325</v>
+        <v>4.39676078643646</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.299241923867385</v>
+        <v>5.35380392829574</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.766605131296387</v>
+        <v>4.846286451170116</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.217312660038097</v>
+        <v>5.320050414309073</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.8728</t>
+          <t>X &gt; 0.8726</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.199308373392718</v>
+        <v>3.216145158353235</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.551656642180212</v>
+        <v>3.588275335767221</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.297137711843135</v>
+        <v>3.334202151921794</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.006605492177641</v>
+        <v>2.905426975259374</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.328063484663993</v>
+        <v>2.276513029838178</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.62543751429908</v>
+        <v>2.549298548657106</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.82123206386882</v>
+        <v>3.047301677308745</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.03719287309751</v>
+        <v>3.978116961618142</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4.116463170992674</v>
+        <v>4.080809156950622</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>4.108059101170532</v>
+        <v>4.094969402951278</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.183862851746241</v>
+        <v>4.309823368823011</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.340260639445184</v>
+        <v>5.345643737472813</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.060362240549729</v>
+        <v>5.090150615378263</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.12761261728398</v>
+        <v>6.17718430420927</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.9132</t>
+          <t>X &gt; 0.913</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.013589463971144</v>
+        <v>2.781858978032723</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>2.841017659300228</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.304335282855575</v>
+        <v>4.089615437408888</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.984010975894485</v>
+        <v>4.766944734098018</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.71312069019806</v>
+        <v>3.547768585846818</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.559945269283695</v>
+        <v>4.367999360140203</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.672306774564383</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.83966809773262</v>
+        <v>5.666328028779581</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.412385574909472</v>
+        <v>5.264391915993144</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.027668243781079</v>
+        <v>5.90041734977671</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.907216169769974</v>
+        <v>4.783868143116521</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.491044871575845</v>
+        <v>5.389480135955871</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.254044201412619</v>
+        <v>5.176803961216862</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.944981316840611</v>
+        <v>6.885702837830763</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.9536</t>
+          <t>X &gt; 0.9533</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.184108600007519</v>
+        <v>3.018143703368551</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.282282112855022</v>
+        <v>4.137669320915393</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.87273240297683</v>
+        <v>4.726732315401669</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.756652127845982</v>
+        <v>4.610916110916108</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.97205715603107</v>
+        <v>3.875966724263947</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.515736604385374</v>
+        <v>4.394452488783116</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.938415407680772</v>
+        <v>3.842395908157158</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.441790113647741</v>
+        <v>5.342165113375785</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.888197119686538</v>
+        <v>4.813792012838498</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.269805416952735</v>
+        <v>5.218464660524745</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.31140967741176</v>
+        <v>5.260024458688896</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.853176992328656</v>
+        <v>4.826790704653305</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.171942395172877</v>
+        <v>5.168733515190219</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>6.875510557714676</v>
+        <v>6.891979851407051</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.994</t>
+          <t>X &gt; 0.9937</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.571348777828021</v>
+        <v>2.35099928622413</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.096051186506351</v>
+        <v>3.892822201068277</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.443440080496948</v>
+        <v>5.23519532386468</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.179937001088796</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.383807726738752</v>
+        <v>5.223052446349662</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.984317644875581</v>
+        <v>4.801393520724147</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.551175229860284</v>
+        <v>4.740737431498687</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>5.826266864819189</v>
+        <v>6.011015782226458</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.113716764045535</v>
+        <v>6.321265395311883</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.263797967715675</v>
+        <v>5.497436814496901</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.452825032451997</v>
+        <v>6.682185255849696</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.835635240556464</v>
+        <v>7.08757421543681</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.71862027574479</v>
+        <v>5.997971844428541</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.731812371964345</v>
+        <v>9.024794484221694</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>195</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.3395967899784722</v>
+        <v>0.3104009956258409</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.882256850760797</v>
+        <v>4.881070064316141</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.104890096773609</v>
+        <v>4.104395604395606</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.181985159062521</v>
+        <v>8.230531078828292</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.940897650236074</v>
+        <v>6.964855059185687</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.876298134362656</v>
+        <v>5.925545696756373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.840957003480902</v>
+        <v>6.914214113260599</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.555140771253605</v>
+        <v>8.654488096548178</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.837619100172901</v>
+        <v>7.937527136191576</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.871997252528224</v>
+        <v>7.995693873556469</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.913384860753276</v>
+        <v>6.062074408531103</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.728864100723392</v>
+        <v>9.900862860290054</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 1.075</t>
+          <t>X &gt; 1.074</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.238092233928455</v>
+        <v>1.588248830850723</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.37070779375719</v>
+        <v>10.66080945061291</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.8023826899939</v>
+        <v>10.2670714622982</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.147483866640101</v>
+        <v>4.659250585480088</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.87365712346176</v>
+        <v>12.36672275600358</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.69169231012165</v>
+        <v>10.18049188137989</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.60698195085548</v>
+        <v>10.11983579215443</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.96635958806048</v>
+        <v>10.47367516291862</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.07893115054597</v>
+        <v>10.43670255378182</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.36124375917478</v>
+        <v>13.71123462870455</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.50365003893111</v>
+        <v>11.86774991887337</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.36447447227818</v>
+        <v>12.74558878738581</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.2914310569813</v>
+        <v>10.7110865985269</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.99650555018304</v>
+        <v>13.41914785398489</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.357142857142847</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>15.34315732023467</v>
+        <v>15.39170324000045</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>13.2595789689174</v>
+        <v>13.28353637786701</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.17486860965123</v>
+        <v>13.22288028864155</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>13.89827615634068</v>
+        <v>13.9475237187344</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>13.8372939998179</v>
+        <v>13.9105511095976</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>16.55880377491661</v>
+        <v>16.65815110021119</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>16.35410261665642</v>
+        <v>16.45401065267509</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>14.00752838805935</v>
+        <v>14.13122500908759</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>12.39690134426976</v>
+        <v>12.54559089204759</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>12.6226369944963</v>
+        <v>12.79463575406296</v>
       </c>
     </row>
   </sheetData>
@@ -3904,209 +3904,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.05597</t>
+          <t>X &lt; -0.05585</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.661941112322786</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.465507444027736</v>
+        <v>1.465354054023415</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>1.595238095238095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.200300177377542</v>
+        <v>8.248846097143314</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1.270106704889322</v>
+        <v>1.318118383879643</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.6540418701547</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.659138278607308</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01559</t>
+          <t>X &lt; -0.01548</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8.676108762854071</v>
+        <v>8.780210755758176</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>5.412030107806778</v>
+        <v>5.584130444795875</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2.537919880076529</v>
+        <v>1.964586004868274</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.4815668202764911</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.262086875527871</v>
+        <v>5.637478969647155</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.600783219212552</v>
+        <v>1.878006423949962</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.342519140938116</v>
+        <v>2.623801947627726</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.354789340126587</v>
+        <v>4.577324025954056</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.9880220596368687</v>
+        <v>1.314544965204362</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.790995825290473</v>
+        <v>2.910071223099052</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.06659789495318336</v>
+        <v>0.7455321393185272</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.858666023589592</v>
+        <v>-0.3691653109748501</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.374075685080463</v>
+        <v>0.875021024756407</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.5998113353069954</v>
+        <v>1.124065886771774</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.0248</t>
+          <t>X &lt; 0.02488</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>186</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.583600098497911</v>
+        <v>5.468611579368336</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2089731452190193</v>
+        <v>0.1620302388933297</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3518361690661322</v>
+        <v>-0.2317077494213748</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.019695721256646</v>
+        <v>0.9620060790273541</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.244847028376007</v>
+        <v>3.66424629977756</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2964886194082652</v>
+        <v>-0.318287330339686</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.6940698385298703</v>
+        <v>0.6848863676689021</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2270011947431314</v>
+        <v>0.7509685009025731</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3716153703817966</v>
+        <v>0.1820809981487628</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.466637876299103</v>
+        <v>2.017826885418884</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1866679008346139</v>
+        <v>0.5194550122371027</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.7586804617920819</v>
+        <v>0.8823770828203266</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3385296084786731</v>
+        <v>0.4872191562565007</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.123906784305554</v>
+        <v>-1.951908024738891</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.06518</t>
+          <t>X &lt; 0.06525</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>251</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.69438277424652</v>
+        <v>3.616370388551751</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.502460689335237</v>
+        <v>-1.524118949568532</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.094799798419686</v>
+        <v>-0.3368292698990416</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5717878069959355</v>
+        <v>-0.6022021456804083</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.475580010426306</v>
+        <v>2.070604049336055</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.211109704958538</v>
+        <v>-1.213922684809447</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.4990073152207231</v>
+        <v>-0.4840649400428134</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1692632100034785</v>
+        <v>0.2358730505619846</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.425464490032226</v>
+        <v>-0.9868703095629527</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1150549606498643</v>
+        <v>0.5608426115983463</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.683271695618295</v>
+        <v>-1.403132204467759</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.648893543262972</v>
+        <v>-1.525196922234727</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.670638022074392</v>
+        <v>-1.521948474296565</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.436934244357815</v>
+        <v>-3.264935484791152</v>
       </c>
     </row>
     <row r="10">
@@ -4119,150 +4119,150 @@
         <v>347</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.291418263413767</v>
+        <v>4.061316746541586</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.08657222798682795</v>
+        <v>-0.0932889100428369</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.420907471473875</v>
+        <v>1.227258815928174</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3983948629008438</v>
+        <v>0.2142857142857082</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.45376525216826</v>
+        <v>2.01075085904808</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.130705098600103</v>
+        <v>-0.002177907847283223</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.07276898017406808</v>
+        <v>0.222880288641548</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9706685396933636</v>
+        <v>-0.5286667574560866</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.608019572296833</v>
+        <v>-1.137067938021453</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.593385054505646</v>
+        <v>-1.233102822561364</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.662639526886885</v>
+        <v>-2.429404782464481</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.628261374531562</v>
+        <v>-2.504564753503317</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.04841222784497</v>
+        <v>-2.899722680067143</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.263598767820156</v>
+        <v>-4.091600008253494</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.1459</t>
+          <t>X &lt; 0.146</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>461</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.785895249292118</v>
+        <v>4.571433239490695</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.873190718050417</v>
+        <v>1.915294780944286</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.647616730258491</v>
+        <v>3.452887264732595</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.042483956276357</v>
+        <v>2.080625383200484</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.154953622269595</v>
+        <v>2.020560791604794</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5845487038436943</v>
+        <v>-0.3800580921790697</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2354195837172313</v>
+        <v>-0.01060665452281739</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.136327706896601</v>
+        <v>-0.6914931783470237</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7634703840267463</v>
+        <v>-0.3956886276766269</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.179549700963975</v>
+        <v>-0.8853025663526353</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.468849557705738</v>
+        <v>-2.268933070268631</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-2.000631925957784</v>
+        <v>-1.876935304929539</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.203863039574884</v>
+        <v>-2.055173491797056</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.628886608437291</v>
+        <v>-2.456887848870629</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.1863</t>
+          <t>X &lt; 0.1864</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>597</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.967995192246221</v>
+        <v>3.874631127020145</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2.021800723973001</v>
+        <v>1.959779083323667</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.474600528497703</v>
+        <v>4.385278242604315</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.929783796039167</v>
+        <v>3.022624970386168</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.061510993362226</v>
+        <v>3.030888267245189</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.013826396531655</v>
+        <v>1.24034700909624</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5941076620561034</v>
+        <v>0.8474650062495144</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1270390182693646</v>
+        <v>0.4739479323466185</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1014473258580963</v>
+        <v>0.1962653953118831</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.118870309792655</v>
+        <v>-0.8690768193372662</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.491075655657525</v>
+        <v>-1.315538638613333</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7866807528834485</v>
+        <v>-0.6629841318552039</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.039327418592165</v>
+        <v>-0.8906378708143379</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.818616893993777</v>
+        <v>-1.646618134427115</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>746</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.417207293862432</v>
+        <v>3.340952004900245</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.671972943425949</v>
+        <v>1.624796196340135</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.226263220869292</v>
+        <v>4.156590122919056</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.613861018613164</v>
+        <v>2.690729483282674</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.1479575244987</v>
+        <v>3.132331406160539</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.300559436171319</v>
+        <v>1.484982069326009</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.349897334277806</v>
+        <v>1.557481772377514</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2125874036278006</v>
+        <v>0.4999046711153525</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1164912676402849</v>
+        <v>0.1366303263310158</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.234506578715454</v>
+        <v>-1.014372454665313</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.305159479602992</v>
+        <v>-1.14495664508739</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.7345882977570568</v>
+        <v>-0.6108916767288122</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.422835665815768</v>
+        <v>-1.27414611803794</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.5992447877072</v>
+        <v>-1.427246028140537</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>920</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.002254436349475</v>
+        <v>2.877819209595778</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.907897876401826</v>
+        <v>0.7558490209916471</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.121822143820694</v>
+        <v>3.056076549918323</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.382482070017758</v>
+        <v>2.431650246305416</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.60506208213944</v>
+        <v>2.588952829491426</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.054610024818011</v>
+        <v>1.197698806592534</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.752508361204022</v>
+        <v>0.8732968267470724</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.5841254999740286</v>
+        <v>-0.3973926261819543</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.079890265192454</v>
+        <v>-0.9162887172422245</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.364591670217962</v>
+        <v>-2.223085034546081</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.025814567608592</v>
+        <v>-1.826642172446277</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.77404511090544</v>
+        <v>-1.600898459192216</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.194195964218849</v>
+        <v>-2.045506416441022</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.294547270514059</v>
+        <v>-2.231244163121303</v>
       </c>
     </row>
     <row r="15">
@@ -4379,98 +4379,98 @@
         <v>1083</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.408382862454573</v>
+        <v>2.301987166863704</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.12488771943044</v>
+        <v>0.9937871669507459</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.392166196171253</v>
+        <v>2.341570718507718</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.968374719260993</v>
+        <v>2.013159617650906</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.261110096913221</v>
+        <v>2.257182704013381</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.8040981616360341</v>
+        <v>0.9309806766874473</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.8117239057863017</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4863696687483667</v>
+        <v>-0.320683564178772</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1780074116053996</v>
+        <v>-0.03127216985217984</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.581942828433867</v>
+        <v>-1.448925984766447</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.601971779861195</v>
+        <v>-1.418493187570675</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.382921420673</v>
+        <v>-1.217571336018707</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.618400067153537</v>
+        <v>-1.46971051937571</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.577336623759876</v>
+        <v>-1.49767396760965</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.3479</t>
+          <t>X &lt; 0.3478</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.74165697656904</v>
+        <v>1.728506699445823</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.121168018581912</v>
+        <v>1.008751906283685</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.069208640145987</v>
+        <v>2.027886759413263</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.120444842186167</v>
+        <v>2.157770800627944</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.898111055283202</v>
+        <v>1.870025912352979</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8526730785991745</v>
+        <v>0.9295381748122011</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6099848362366487</v>
+        <v>0.6765163457394436</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.5679842814837457</v>
+        <v>-0.4544260375460709</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5499774964583324</v>
+        <v>-0.4483366535454891</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.557874175884564</v>
+        <v>-1.46562838003517</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.762575334144756</v>
+        <v>-1.547830967951057</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.96516400643398</v>
+        <v>-1.762478443857553</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.306325918199207</v>
+        <v>-2.114676376915334</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.843623443328127</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9030618700181279</v>
+        <v>0.8552727904976294</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7109386504170203</v>
+        <v>0.6457220789681557</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.352794770845122</v>
+        <v>1.350885189554546</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.483019914433484</v>
+        <v>1.549450549450547</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.497598364102124</v>
+        <v>1.510996318056421</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.034778889936248</v>
+        <v>1.13478416721658</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4663090282512812</v>
+        <v>0.5618833365227687</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.415410617608714</v>
+        <v>-0.2791586897661986</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.6146097748225756</v>
+        <v>-0.485103775375002</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.533637071497971</v>
+        <v>-1.409172380905403</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.461904228376</v>
+        <v>-1.299612535730709</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.049502579130554</v>
+        <v>-1.89416304668719</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.64035142829745</v>
+        <v>-1.491661880519622</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.445728941089556</v>
+        <v>-1.380834019195341</v>
       </c>
     </row>
     <row r="18">
@@ -4532,777 +4532,777 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.68285568162446</v>
+        <v>0.6708640861692245</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.3461349962031903</v>
+        <v>0.2612509293642091</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3238030900328752</v>
+        <v>0.2998785988629677</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.8607429395829698</v>
+        <v>0.862128297891104</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.8814595976674013</v>
+        <v>0.8396401403477398</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.930386422333541</v>
+        <v>0.9613347699511152</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1343820607743638</v>
+        <v>0.1305889166471985</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7055890068781281</v>
+        <v>-0.6728507468413127</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.015172779311406</v>
+        <v>-0.9858907385171136</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.367888343820255</v>
+        <v>-1.342173642209033</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.572589502080447</v>
+        <v>-1.512431507315455</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.035414581546135</v>
+        <v>-1.978999341360208</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.675593325239831</v>
+        <v>-1.657307658677055</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.540103397242234</v>
+        <v>-1.59459820038839</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.469</t>
+          <t>X &lt; 0.4689</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1785</v>
+        <v>1789</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.4138769243891005</v>
+        <v>-0.4522697781684144</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.8780160419883458</v>
+        <v>-0.9230998110439472</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.7138159342894994</v>
+        <v>-0.7050469206044809</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.05016066901541905</v>
+        <v>-0.01898935324964413</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3064043640186398</v>
+        <v>0.3010760041311471</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7156352169199494</v>
+        <v>0.7716051020159114</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4573162172733944</v>
+        <v>-0.4281344347965756</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9803445700696471</v>
+        <v>-0.9194933221956987</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.09728643560193</v>
+        <v>-1.037792979850792</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.611446977874706</v>
+        <v>-1.552414375979296</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.648269009106365</v>
+        <v>-1.558671807243549</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.2854073648652</v>
+        <v>-2.196255703867969</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.947470222946151</v>
+        <v>-1.890513342826907</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.971200540517714</v>
+        <v>-1.976851376283875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.5094</t>
+          <t>X &lt; 0.5093</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1932</v>
+        <v>1938</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5985024152687544</v>
+        <v>-0.6354328315639179</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5317306065703207</v>
+        <v>-0.5750557307927053</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.307306944885724</v>
+        <v>-0.3010998310745379</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1090201948634331</v>
+        <v>0.1369506200014641</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3967502597336718</v>
+        <v>0.3951290707644191</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7743369382208201</v>
+        <v>0.7991441633976635</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3670287694554588</v>
+        <v>-0.3647152433984289</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7307382401155778</v>
+        <v>-0.6996835944533686</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9467591563282838</v>
+        <v>-0.914616856662029</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.538280019841601</v>
+        <v>-1.5044307795268</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.794660764665103</v>
+        <v>-1.732047275650878</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.404300045485719</v>
+        <v>-2.36782948635679</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.865409891657613</v>
+        <v>-1.858065307274245</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.077155966166238</v>
+        <v>-2.125016317291909</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.5498</t>
+          <t>X &lt; 0.5497</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2080</v>
+        <v>2086</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7567780994998685</v>
+        <v>-0.7695300413867443</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.049457178701203</v>
+        <v>-1.065153478473924</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.4600278707693235</v>
+        <v>-0.4574608516241199</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.3038905709998758</v>
+        <v>-0.3017993456924799</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.218678925054796</v>
+        <v>-0.2401867474981216</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.03902262143083846</v>
+        <v>-0.03683475052704921</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9616789522443909</v>
+        <v>-0.9792219569389573</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.044686146199155</v>
+        <v>-1.036997814544314</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.297699027637925</v>
+        <v>-1.28723532204824</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.95558709905179</v>
+        <v>-1.941757762855566</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.064272894853993</v>
+        <v>-2.024299771542466</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.676292114204948</v>
+        <v>-2.658594366938672</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-2.30184696812583</v>
+        <v>-2.309407168508692</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.626905130045834</v>
+        <v>-2.657585402856192</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.5902</t>
+          <t>X &lt; 0.59</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2217</v>
+        <v>2224</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8636653566799097</v>
+        <v>-0.8770022052001849</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.01345043820492</v>
+        <v>-1.028411952548424</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4401109184251624</v>
+        <v>-0.437809896120406</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3305574965687299</v>
+        <v>-0.3284946924159158</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1244608701557866</v>
+        <v>-0.1665890424297558</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.06249914644360643</v>
+        <v>0.04108886122594413</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.7633553285727075</v>
+        <v>-0.8019003990705684</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6898834318189131</v>
+        <v>-0.705476494803932</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.426541264017374</v>
+        <v>-1.435856632503281</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.871054654941815</v>
+        <v>-1.876515908423507</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.120800858247051</v>
+        <v>-2.101274056628476</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.55774125292006</v>
+        <v>-2.557903472493706</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.187237090184269</v>
+        <v>-2.209893324110787</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.568419130254007</v>
+        <v>-2.610896962620835</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.6305</t>
+          <t>X &lt; 0.6304</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2366</v>
+        <v>2371</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.649337083165932</v>
+        <v>-0.6629245872715401</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.059246184255301</v>
+        <v>-1.070618884853928</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5045726233974719</v>
+        <v>-0.4987817262332825</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4359063748828973</v>
+        <v>-0.4722205555888905</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.2766334049967867</v>
+        <v>-0.3505936787670549</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1671841413900239</v>
+        <v>-0.2230390139542919</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.6932493424684125</v>
+        <v>-0.7654652598385709</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.8648346599571326</v>
+        <v>-0.9141466540844903</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.390147757805373</v>
+        <v>-1.433364234317743</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.986795131594079</v>
+        <v>-2.024054413573275</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.022648674826826</v>
+        <v>-2.0369830489336</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.429891174360201</v>
+        <v>-2.4616953448947</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.193598987675443</v>
+        <v>-2.244018037527617</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.494297353207287</v>
+        <v>-2.562557312957189</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.6709</t>
+          <t>X &lt; 0.6708</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2530</v>
+        <v>2539</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7689915913371905</v>
+        <v>-0.7846216288085586</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.139346218086374</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.607393398073576</v>
+        <v>-0.6046739571810704</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4559391449067007</v>
+        <v>-0.4536512918231352</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1452335426142</v>
+        <v>-0.1760623277651163</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3388888093611158</v>
+        <v>-0.3529547321223419</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.71777720607151</v>
+        <v>-0.7458100940315546</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.084623080702208</v>
+        <v>-1.111883148138091</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.421848331147636</v>
+        <v>-1.442099384562333</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.956060734423041</v>
+        <v>-1.969547718207252</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.863050016208803</v>
+        <v>-1.877074731911478</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.360108714174899</v>
+        <v>-2.387861964544825</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.047793957794163</v>
+        <v>-2.092579336673815</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.274784424664254</v>
+        <v>-2.334117598400518</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.7113</t>
+          <t>X &lt; 0.7111</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2700</v>
+        <v>2709</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8394553149312571</v>
+        <v>-0.8379324790582459</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.9186703892808339</v>
+        <v>-0.9143105932475351</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4447915592945222</v>
+        <v>-0.4429092512987225</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4053928256215755</v>
+        <v>-0.4034834235275611</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1479855720903274</v>
+        <v>-0.1738386500447433</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.08906425777461635</v>
+        <v>-0.1017625337477028</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8190579813178829</v>
+        <v>-0.841920889561699</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.192242299562395</v>
+        <v>-1.214275807706024</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-1.378777591669206</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.696338518687227</v>
+        <v>-1.703616754737645</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.732943522553981</v>
+        <v>-1.740258205310582</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.011469884824919</v>
+        <v>-2.030883508240386</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.634057207236744</v>
+        <v>-1.66807981608806</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.869426497567197</v>
+        <v>-1.915589421278497</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.7517</t>
+          <t>X &lt; 0.7515</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2876</v>
+        <v>2884</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4545911257889372</v>
+        <v>-0.472819007207427</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5924486239446836</v>
+        <v>-0.605719849269363</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2407729884225489</v>
+        <v>-0.2555933923126403</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1957607087315765</v>
+        <v>-0.2106328364103121</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0478300321914773</v>
+        <v>0.01015829571787208</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2948719202408796</v>
+        <v>0.26733404631198</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.152597052073375</v>
+        <v>-0.189433789532103</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6701762246117084</v>
+        <v>-0.7056316610645865</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.765880603356706</v>
+        <v>-0.7930042481633706</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.199132733019894</v>
+        <v>-1.217129205817045</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.280575429622878</v>
+        <v>-1.298393391727565</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.539809379570279</v>
+        <v>-1.567715689853088</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.211023577523775</v>
+        <v>-1.250728328881685</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.522339494012883</v>
+        <v>-1.571984680518646</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.7921</t>
+          <t>X &lt; 0.7919</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3083</v>
+        <v>3090</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2831138327321483</v>
+        <v>-0.2703438584029314</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.6811742218846391</v>
+        <v>-0.676138684381975</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.4441826933467539</v>
+        <v>-0.4399453117725614</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3935296329628528</v>
+        <v>-0.3894009216589893</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.121243311912913</v>
+        <v>0.1068187150384929</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1450712687832834</v>
+        <v>0.1391114032289948</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4400462682170172</v>
+        <v>-0.4527966337257254</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.8247559136301703</v>
+        <v>-0.8365294374117909</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8857380701529465</v>
+        <v>-0.8882795696854302</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.282142127253785</v>
+        <v>-1.27440653822881</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.307070731490356</v>
+        <v>-1.299210907529975</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.54661223091108</v>
+        <v>-1.546714989680332</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.430224836942017</v>
+        <v>-1.406589786111731</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.575809169567776</v>
+        <v>-1.560426659251881</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.8325</t>
+          <t>X &lt; 0.8322</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3277</v>
+        <v>3287</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.7630686605130634</v>
+        <v>-0.752536067311226</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.8074305907514656</v>
+        <v>-0.8044134932498679</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7296480748272103</v>
+        <v>-0.7271724411107243</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5526313227685122</v>
+        <v>-0.5506521079769442</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1613001705241786</v>
+        <v>-0.1740619010074056</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2126674205031804</v>
+        <v>-0.2185230194882948</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.5549516766722675</v>
+        <v>-0.5662601398431448</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7008358833563761</v>
+        <v>-0.7119993677549914</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6842659194866059</v>
+        <v>-0.7020740133555989</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9246144628448221</v>
+        <v>-0.9320299129415659</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.9905547584887628</v>
+        <v>-0.9978637140928939</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.244290546284731</v>
+        <v>-1.25737190124844</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.098551748498771</v>
+        <v>-1.118816476739347</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.252568260019309</v>
+        <v>-1.278842739859712</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.8728</t>
+          <t>X &lt; 0.8726</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3453</v>
+        <v>3461</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6344070865066485</v>
+        <v>-0.6390697984045417</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5856086171046826</v>
+        <v>-0.5948725553062957</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5896448709398214</v>
+        <v>-0.598778050431271</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5016093812245757</v>
+        <v>-0.4821788698193217</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3599870224243915</v>
+        <v>-0.3507147646653834</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.393576601314173</v>
+        <v>-0.3793141760184326</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4048176000927839</v>
+        <v>-0.4531783701160776</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6827340447909549</v>
+        <v>-0.672636430701786</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6701284023413479</v>
+        <v>-0.665054089204375</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6653928172290691</v>
+        <v>-0.66508122302114</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6804542616504534</v>
+        <v>-0.7089168739937648</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.9194235794135892</v>
+        <v>-0.9235032061950434</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8603297473562392</v>
+        <v>-0.8694458332144421</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.11076253386414</v>
+        <v>-1.12440773735846</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.9132</t>
+          <t>X &lt; 0.913</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3620</v>
+        <v>3629</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4302691821996376</v>
+        <v>-0.3958888704663295</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3200756918801275</v>
+        <v>-0.2893888825778603</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5623348137787261</v>
+        <v>-0.5309829423135852</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6376401003020504</v>
+        <v>-0.6061123542574478</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4446761377558417</v>
+        <v>-0.4208834769293048</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.5457447041019847</v>
+        <v>-0.5180661988249327</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5604104482084793</v>
+        <v>-0.5363527775222181</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7367670501310997</v>
+        <v>-0.7121998680868558</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6448078064218379</v>
+        <v>-0.6241345313070923</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7346367801133482</v>
+        <v>-0.7172961885309022</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5652486181792185</v>
+        <v>-0.5482968782667967</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.653537584436755</v>
+        <v>-0.6400566790214057</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6164730195602743</v>
+        <v>-0.6067113511637459</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9001201746697163</v>
+        <v>-0.8933800970832309</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.9536</t>
+          <t>X &lt; 0.9533</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3760</v>
+        <v>3770</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.3208312173883172</v>
+        <v>-0.302868895994564</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3275209995260724</v>
+        <v>-0.312220692168701</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4428533545478572</v>
+        <v>-0.4272543514122873</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.4043937228550476</v>
+        <v>-0.3888888888888928</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3181270927079964</v>
+        <v>-0.3081543690923993</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3512793871638991</v>
+        <v>-0.3385614819227527</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2623114123443031</v>
+        <v>-0.2524780834602751</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4493959980229292</v>
+        <v>-0.4390783797321163</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3630474913602484</v>
+        <v>-0.3556109843790694</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4013703053424891</v>
+        <v>-0.3965086015073425</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4052585819819541</v>
+        <v>-0.4003934466269641</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3560320281326312</v>
+        <v>-0.3539540041932128</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3890851588132662</v>
+        <v>-0.3895911362131983</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6005139680163722</v>
+        <v>-0.6031159195507882</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.994</t>
+          <t>X &lt; 0.9937</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3879</v>
+        <v>3889</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1684802648611807</v>
+        <v>-0.1523465762965159</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1728011726858156</v>
+        <v>-0.1584004199120983</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3223490867593881</v>
+        <v>-0.307539718870359</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2039098715789578</v>
+        <v>-0.1894075403949742</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2910284528399814</v>
+        <v>-0.2799476676689281</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2368744104791247</v>
+        <v>-0.2241068641873269</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1789289052373846</v>
+        <v>-0.1938108231214315</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2973480392835128</v>
+        <v>-0.3119053417216264</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.292714337193523</v>
+        <v>-0.3091275168606913</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2271251214938772</v>
+        <v>-0.2455099275186825</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3144040441222629</v>
+        <v>-0.3325600907301833</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3429090298864281</v>
+        <v>-0.3628455566868993</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2589651260297003</v>
+        <v>-0.2809484640547524</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5085087352573225</v>
+        <v>-0.5317181868448557</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3971</v>
+        <v>3982</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.004023728501792334</v>
+        <v>0.005532730807637165</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1126896204598467</v>
+        <v>-0.1123174528570559</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1925490482828991</v>
+        <v>-0.1920106198701887</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.09892417486282312</v>
+        <v>-0.09862582307472678</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2969479681118017</v>
+        <v>-0.2986596001995139</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2120398872201861</v>
+        <v>-0.2127042236367558</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1825256300959595</v>
+        <v>-0.1845257923669408</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1581434947483302</v>
+        <v>-0.1602758705095297</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1801439612820346</v>
+        <v>-0.1834687406299267</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2615017057662357</v>
+        <v>-0.2659642559162165</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2256898438607564</v>
+        <v>-0.2302816338756628</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2275464624194683</v>
+        <v>-0.2333762531040264</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1300731917682256</v>
+        <v>-0.1374788208991049</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3433905144675009</v>
+        <v>-0.3514262870267117</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 1.075</t>
+          <t>X &lt; 1.074</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4045</v>
+        <v>4055</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01664791816372713</v>
+        <v>-0.02731929784667386</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1852744183972916</v>
+        <v>-0.1960673708247356</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2462423446451325</v>
+        <v>-0.2322310301824331</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.05331914158359297</v>
+        <v>-0.03979968371113074</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2822097481516295</v>
+        <v>-0.2696203445514698</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.193418810505257</v>
+        <v>-0.1803010399453129</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1659859947769249</v>
+        <v>-0.1537111160148541</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1999476802193811</v>
+        <v>-0.1875122212756963</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1485966527394211</v>
+        <v>-0.1616984798933743</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2439929179763993</v>
+        <v>-0.2575213032660955</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1878699035769671</v>
+        <v>-0.2015081344356133</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2137642802310893</v>
+        <v>-0.2281421047779091</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1504705456626851</v>
+        <v>-0.1657362423564734</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2568732768557567</v>
+        <v>-0.2727120235190981</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.002283551901868464</v>
+        <v>-0.001587713829998449</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.01296191841986882</v>
+        <v>-0.01289914146792626</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1257691838968285</v>
+        <v>-0.1254284578117293</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.03113516828392449</v>
+        <v>-0.03104000557083708</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2139308291291897</v>
+        <v>-0.2145051136481655</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1476861376142224</v>
+        <v>-0.1478566621580768</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1212568838330412</v>
+        <v>-0.1220674465500906</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1591276270905055</v>
+        <v>-0.1598660046592357</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1332513996484721</v>
+        <v>-0.1346277232825486</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1865287193145591</v>
+        <v>-0.1883800433665783</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1817136682418692</v>
+        <v>-0.1835916538725257</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1336030890172637</v>
+        <v>-0.1361742583116623</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.09916247435100445</v>
+        <v>-0.1024189713994943</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1290486871256888</v>
+        <v>-0.132778065117293</v>
       </c>
     </row>
   </sheetData>
